--- a/results/radial_T_right.xlsx
+++ b/results/radial_T_right.xlsx
@@ -437,701 +437,1101 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>5975.0224335999</v>
+      </c>
+      <c r="C2" t="n">
+        <v>436.0153424180646</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>0.02097979797979798</v>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>5976.483440810643</v>
+      </c>
+      <c r="C3" t="n">
+        <v>432.6340136305364</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0.04195959595959596</v>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>5977.683350030858</v>
+      </c>
+      <c r="C4" t="n">
+        <v>429.3835875150403</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>0.06293939393939393</v>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>5978.60825841264</v>
+      </c>
+      <c r="C5" t="n">
+        <v>426.3266121480419</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>0.08391919191919192</v>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>5979.243865526048</v>
+      </c>
+      <c r="C6" t="n">
+        <v>423.5263182420726</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>0.1048989898989899</v>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>5979.575396575801</v>
+      </c>
+      <c r="C7" t="n">
+        <v>421.0468458977961</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>0.1258787878787879</v>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>5979.587513062448</v>
+      </c>
+      <c r="C8" t="n">
+        <v>418.9534745673844</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>0.1468585858585859</v>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>5979.264209569993</v>
+      </c>
+      <c r="C9" t="n">
+        <v>417.3128580357806</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>0.1678383838383838</v>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>5978.588695040206</v>
+      </c>
+      <c r="C10" t="n">
+        <v>416.1932663666528</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>0.1888181818181818</v>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>5977.543256527786</v>
+      </c>
+      <c r="C11" t="n">
+        <v>415.6648369455991</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>0.2097979797979798</v>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>5976.109103007231</v>
+      </c>
+      <c r="C12" t="n">
+        <v>415.7998370012074</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>0.2307777777777778</v>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>5974.337541093772</v>
+      </c>
+      <c r="C13" t="n">
+        <v>416.5592133762611</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>0.2517575757575757</v>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>5972.501825190653</v>
+      </c>
+      <c r="C14" t="n">
+        <v>417.7298116094724</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>0.2727373737373737</v>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>5970.607242049798</v>
+      </c>
+      <c r="C15" t="n">
+        <v>419.3534310486251</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>0.2937171717171717</v>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>5968.524530085347</v>
+      </c>
+      <c r="C16" t="n">
+        <v>421.289869105273</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>0.3146969696969697</v>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>5966.117075472211</v>
+      </c>
+      <c r="C17" t="n">
+        <v>423.3956521760683</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>0.3356767676767677</v>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>5963.148368838366</v>
+      </c>
+      <c r="C18" t="n">
+        <v>425.5115544918795</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>0.3566565656565657</v>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>5959.496091714745</v>
+      </c>
+      <c r="C19" t="n">
+        <v>427.4925353906402</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>0.3776363636363637</v>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>5955.097076443844</v>
+      </c>
+      <c r="C20" t="n">
+        <v>429.1998129530964</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>0.3986161616161616</v>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>5949.884850093269</v>
+      </c>
+      <c r="C21" t="n">
+        <v>430.4914143824956</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>0.4195959595959596</v>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>5943.788735121068</v>
+      </c>
+      <c r="C22" t="n">
+        <v>431.2211502223228</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>0.4405757575757576</v>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>5936.732753326794</v>
+      </c>
+      <c r="C23" t="n">
+        <v>431.2372821999722</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>0.4615555555555556</v>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>5928.713430676257</v>
+      </c>
+      <c r="C24" t="n">
+        <v>430.2551618905309</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>0.4825353535353535</v>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>5920.285623564573</v>
+      </c>
+      <c r="C25" t="n">
+        <v>428.0800376313587</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>0.5035151515151515</v>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>5912.003624804486</v>
+      </c>
+      <c r="C26" t="n">
+        <v>425.6033677529034</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>0.5244949494949495</v>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>5903.925224852729</v>
+      </c>
+      <c r="C27" t="n">
+        <v>422.936867142097</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>0.5454747474747474</v>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>5896.098575130089</v>
+      </c>
+      <c r="C28" t="n">
+        <v>420.1755375981427</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>0.5664545454545454</v>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>5888.573089834988</v>
+      </c>
+      <c r="C29" t="n">
+        <v>417.417853342253</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>0.5874343434343434</v>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>5881.39991688163</v>
+      </c>
+      <c r="C30" t="n">
+        <v>414.7663945045842</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>0.6084141414141414</v>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>5874.632469842216</v>
+      </c>
+      <c r="C31" t="n">
+        <v>412.3286128362421</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>0.6293939393939394</v>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>5868.237287301143</v>
+      </c>
+      <c r="C32" t="n">
+        <v>410.2052331317847</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>0.6503737373737374</v>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>5861.568179471628</v>
+      </c>
+      <c r="C33" t="n">
+        <v>408.4183355209385</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>0.6713535353535354</v>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>5854.448435437444</v>
+      </c>
+      <c r="C34" t="n">
+        <v>407.0634450516507</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>0.6923333333333334</v>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>5846.88408333622</v>
+      </c>
+      <c r="C35" t="n">
+        <v>406.1750346464005</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>0.7133131313131313</v>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+      <c r="B36" t="n">
+        <v>5839.182818134995</v>
+      </c>
+      <c r="C36" t="n">
+        <v>405.3092870830217</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>0.7342929292929293</v>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>5831.315211499426</v>
+      </c>
+      <c r="C37" t="n">
+        <v>404.2438914323631</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>0.7552727272727273</v>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>5823.21605183965</v>
+      </c>
+      <c r="C38" t="n">
+        <v>402.8826237019493</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>0.7762525252525253</v>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+      <c r="B39" t="n">
+        <v>5814.915143766757</v>
+      </c>
+      <c r="C39" t="n">
+        <v>401.3082047760989</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>0.7972323232323233</v>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>5806.444468914768</v>
+      </c>
+      <c r="C40" t="n">
+        <v>399.6087932587516</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>0.8182121212121213</v>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+      <c r="B41" t="n">
+        <v>5797.838461143314</v>
+      </c>
+      <c r="C41" t="n">
+        <v>397.8785953554484</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>0.8391919191919193</v>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>5789.13427936787</v>
+      </c>
+      <c r="C42" t="n">
+        <v>396.2184937246928</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>0.8601717171717171</v>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
+      <c r="B43" t="n">
+        <v>5780.372072949332</v>
+      </c>
+      <c r="C43" t="n">
+        <v>394.7366909270571</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>0.8811515151515151</v>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+      <c r="B44" t="n">
+        <v>5771.595232885838</v>
+      </c>
+      <c r="C44" t="n">
+        <v>393.5493611149967</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>0.9021313131313131</v>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>5762.850620101584</v>
+      </c>
+      <c r="C45" t="n">
+        <v>392.7813012795793</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>0.9231111111111111</v>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>5754.187831951203</v>
+      </c>
+      <c r="C46" t="n">
+        <v>392.5680525264239</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>0.9440909090909091</v>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
+      <c r="B47" t="n">
+        <v>5745.654437732074</v>
+      </c>
+      <c r="C47" t="n">
+        <v>393.0643532283962</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>0.9650707070707071</v>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>5737.162035476138</v>
+      </c>
+      <c r="C48" t="n">
+        <v>394.0819221902975</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>0.9860505050505051</v>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>5728.520431750037</v>
+      </c>
+      <c r="C49" t="n">
+        <v>395.2344162494065</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>1.007030303030303</v>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>5719.691883220881</v>
+      </c>
+      <c r="C50" t="n">
+        <v>396.5108833113108</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>1.028010101010101</v>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>5710.637150894339</v>
+      </c>
+      <c r="C51" t="n">
+        <v>397.9013275045389</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>1.048989898989899</v>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
+      <c r="B52" t="n">
+        <v>5701.314606011353</v>
+      </c>
+      <c r="C52" t="n">
+        <v>399.3949943167649</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>1.069969696969697</v>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
+      <c r="B53" t="n">
+        <v>5691.680020489879</v>
+      </c>
+      <c r="C53" t="n">
+        <v>400.9802835590224</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>1.090949494949495</v>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>5681.6863450703</v>
+      </c>
+      <c r="C54" t="n">
+        <v>402.6446550841614</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>1.111929292929293</v>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>5671.283474485302</v>
+      </c>
+      <c r="C55" t="n">
+        <v>404.3745265485809</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>1.132909090909091</v>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
+      <c r="B56" t="n">
+        <v>5660.417998965057</v>
+      </c>
+      <c r="C56" t="n">
+        <v>406.155162432959</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>1.153888888888889</v>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>5649.054503830881</v>
+      </c>
+      <c r="C57" t="n">
+        <v>407.9362937090632</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>1.174868686868687</v>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>5637.418357333527</v>
+      </c>
+      <c r="C58" t="n">
+        <v>409.2460907400736</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>1.195848484848485</v>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>5625.534105831736</v>
+      </c>
+      <c r="C59" t="n">
+        <v>409.9459791083885</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>1.216828282828283</v>
       </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
+      <c r="B60" t="n">
+        <v>5613.337985053059</v>
+      </c>
+      <c r="C60" t="n">
+        <v>410.0578502501226</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>1.237808080808081</v>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
+      <c r="B61" t="n">
+        <v>5600.752301401228</v>
+      </c>
+      <c r="C61" t="n">
+        <v>409.5902903510652</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>1.258787878787879</v>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>5587.693812885664</v>
+      </c>
+      <c r="C62" t="n">
+        <v>408.5537229470084</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>1.279767676767677</v>
       </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>5574.130843540614</v>
+      </c>
+      <c r="C63" t="n">
+        <v>406.9693330335306</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>1.300747474747475</v>
       </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>5560.038940447465</v>
+      </c>
+      <c r="C64" t="n">
+        <v>404.8628525891687</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>1.321727272727273</v>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
+      <c r="B65" t="n">
+        <v>5545.367808622229</v>
+      </c>
+      <c r="C65" t="n">
+        <v>402.2600209715894</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>1.342707070707071</v>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
+      <c r="B66" t="n">
+        <v>5530.061508534182</v>
+      </c>
+      <c r="C66" t="n">
+        <v>399.1898850688965</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>1.363686868686869</v>
       </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>5514.057753297035</v>
+      </c>
+      <c r="C67" t="n">
+        <v>395.6851175800762</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>1.384666666666667</v>
       </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
+      <c r="B68" t="n">
+        <v>5497.303336954123</v>
+      </c>
+      <c r="C68" t="n">
+        <v>391.756537483491</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>1.405646464646465</v>
       </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
+      <c r="B69" t="n">
+        <v>5480.096359308281</v>
+      </c>
+      <c r="C69" t="n">
+        <v>386.8470909423675</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>1.426626262626263</v>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
+      <c r="B70" t="n">
+        <v>5462.53198585857</v>
+      </c>
+      <c r="C70" t="n">
+        <v>380.7130846233845</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>1.447606060606061</v>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
+      <c r="B71" t="n">
+        <v>5445.265693372108</v>
+      </c>
+      <c r="C71" t="n">
+        <v>374.690663696711</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>1.468585858585859</v>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
+      <c r="B72" t="n">
+        <v>5428.853458125338</v>
+      </c>
+      <c r="C72" t="n">
+        <v>369.9423232635739</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>1.489565656565657</v>
       </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
+      <c r="B73" t="n">
+        <v>5413.190556934747</v>
+      </c>
+      <c r="C73" t="n">
+        <v>366.4133017357839</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>1.510545454545455</v>
       </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
+      <c r="B74" t="n">
+        <v>5398.152805714164</v>
+      </c>
+      <c r="C74" t="n">
+        <v>364.0341357929535</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
         <v>1.531525252525253</v>
       </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
+      <c r="B75" t="n">
+        <v>5383.595074312664</v>
+      </c>
+      <c r="C75" t="n">
+        <v>362.7202600317686</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>1.552505050505051</v>
       </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
+      <c r="B76" t="n">
+        <v>5369.349551613992</v>
+      </c>
+      <c r="C76" t="n">
+        <v>362.3716105520215</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
         <v>1.573484848484848</v>
       </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
+      <c r="B77" t="n">
+        <v>5355.210949468093</v>
+      </c>
+      <c r="C77" t="n">
+        <v>362.8704389055214</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>1.594464646464647</v>
       </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
+      <c r="B78" t="n">
+        <v>5340.819466131005</v>
+      </c>
+      <c r="C78" t="n">
+        <v>364.0650531567343</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
         <v>1.615444444444444</v>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
+      <c r="B79" t="n">
+        <v>5325.866146087327</v>
+      </c>
+      <c r="C79" t="n">
+        <v>365.7815741762672</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
         <v>1.636424242424243</v>
       </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
+      <c r="B80" t="n">
+        <v>5310.476667226028</v>
+      </c>
+      <c r="C80" t="n">
+        <v>367.1273761911473</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
         <v>1.65740404040404</v>
       </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
+      <c r="B81" t="n">
+        <v>5294.654835576003</v>
+      </c>
+      <c r="C81" t="n">
+        <v>367.3143474899389</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
         <v>1.678383838383839</v>
       </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
+      <c r="B82" t="n">
+        <v>5278.63007755208</v>
+      </c>
+      <c r="C82" t="n">
+        <v>366.698843314406</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
         <v>1.699363636363636</v>
       </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
+      <c r="B83" t="n">
+        <v>5262.911185596288</v>
+      </c>
+      <c r="C83" t="n">
+        <v>366.1512833745776</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
         <v>1.720343434343434</v>
       </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
+      <c r="B84" t="n">
+        <v>5247.555699691404</v>
+      </c>
+      <c r="C84" t="n">
+        <v>365.6886421494929</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
         <v>1.741323232323232</v>
       </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
+      <c r="B85" t="n">
+        <v>5232.626679180274</v>
+      </c>
+      <c r="C85" t="n">
+        <v>365.3271883980977</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
         <v>1.76230303030303</v>
       </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
+      <c r="B86" t="n">
+        <v>5218.194678586206</v>
+      </c>
+      <c r="C86" t="n">
+        <v>365.0850197957042</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
         <v>1.783282828282828</v>
       </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
+      <c r="B87" t="n">
+        <v>5204.338501688366</v>
+      </c>
+      <c r="C87" t="n">
+        <v>364.98222660146</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>1.804262626262626</v>
       </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
+      <c r="B88" t="n">
+        <v>5191.146002092391</v>
+      </c>
+      <c r="C88" t="n">
+        <v>365.0410595539349</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
         <v>1.825242424242424</v>
       </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
+      <c r="B89" t="n">
+        <v>5178.714924416114</v>
+      </c>
+      <c r="C89" t="n">
+        <v>365.2860989827072</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
         <v>1.846222222222222</v>
       </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
+      <c r="B90" t="n">
+        <v>5167.15916763973</v>
+      </c>
+      <c r="C90" t="n">
+        <v>365.7358411269458</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
         <v>1.86720202020202</v>
       </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
+      <c r="B91" t="n">
+        <v>5157.526075465998</v>
+      </c>
+      <c r="C91" t="n">
+        <v>364.9444444365689</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
         <v>1.888181818181818</v>
       </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>5150.643852878232</v>
+      </c>
+      <c r="C92" t="n">
+        <v>361.836925248409</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
         <v>1.909161616161616</v>
       </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
+      <c r="B93" t="n">
+        <v>5146.609640231875</v>
+      </c>
+      <c r="C93" t="n">
+        <v>356.8831909871107</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
         <v>1.930141414141414</v>
       </c>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
+      <c r="B94" t="n">
+        <v>5145.473801987433</v>
+      </c>
+      <c r="C94" t="n">
+        <v>350.8802797836808</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
         <v>1.951121212121212</v>
       </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>5147.352355617672</v>
+      </c>
+      <c r="C95" t="n">
+        <v>343.9364680572268</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
         <v>1.97210101010101</v>
       </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>5152.33769797557</v>
+      </c>
+      <c r="C96" t="n">
+        <v>336.1786518066829</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
         <v>1.993080808080808</v>
       </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
+      <c r="B97" t="n">
+        <v>5160.496630482557</v>
+      </c>
+      <c r="C97" t="n">
+        <v>327.7614211654175</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
         <v>2.014060606060606</v>
       </c>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
+      <c r="B98" t="n">
+        <v>5171.870793199566</v>
+      </c>
+      <c r="C98" t="n">
+        <v>318.8642161859688</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
         <v>2.035040404040404</v>
       </c>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
+      <c r="B99" t="n">
+        <v>5186.478182651778</v>
+      </c>
+      <c r="C99" t="n">
+        <v>309.6874947408068</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
         <v>2.056020202020202</v>
       </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
+      <c r="B100" t="n">
+        <v>5204.31565364891</v>
+      </c>
+      <c r="C100" t="n">
+        <v>300.4482367496789</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
         <v>2.077</v>
       </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>5225.362259436593</v>
+      </c>
+      <c r="C101" t="n">
+        <v>291.3751740542384</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/radial_T_right.xlsx
+++ b/results/radial_T_right.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,25 +425,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Radius_mm</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>T_K</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>T_err</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Intercept_b</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Intercept_b_err</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Partition_func</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Partition_func_err</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Electron_concentration</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Electron_concentration_err</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -443,6 +485,24 @@
       <c r="C2" t="n">
         <v>436.0153424180646</v>
       </c>
+      <c r="D2" t="n">
+        <v>42.45879900056699</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7816433797668262</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11.03705204749668</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.204715881985064</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.289362620998454e+21</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.806828629959155e+21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -454,6 +514,24 @@
       <c r="C3" t="n">
         <v>432.6340136305364</v>
       </c>
+      <c r="D3" t="n">
+        <v>42.45608161327682</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7752025318951238</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11.04109028165649</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.196151733866501</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.283985339416603e+21</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.787757680859141e+21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -465,6 +543,24 @@
       <c r="C4" t="n">
         <v>429.3835875150403</v>
       </c>
+      <c r="D4" t="n">
+        <v>42.45343879200961</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7690695055593569</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11.04440867401985</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.187799747817352</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.278641782127393e+21</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.769485863616299e+21</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -476,6 +572,24 @@
       <c r="C5" t="n">
         <v>426.3266121480419</v>
       </c>
+      <c r="D5" t="n">
+        <v>42.45089408496061</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7633579107055515</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11.04696777742271</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.179828270898243</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.273377320723783e+21</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.752303214846213e+21</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -487,6 +601,24 @@
       <c r="C6" t="n">
         <v>423.5263182420726</v>
       </c>
+      <c r="D6" t="n">
+        <v>42.44847146165682</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7581826336094584</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11.04872698902483</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.172410286608973</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.26823760543373e+21</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.736499680754814e+21</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -498,6 +630,24 @@
       <c r="C7" t="n">
         <v>421.0468458977961</v>
       </c>
+      <c r="D7" t="n">
+        <v>42.44619543974098</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.753660386530566</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11.049644842682</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.165718977337093</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.263268919013235e+21</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.722366791270159e+21</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -509,6 +659,24 @@
       <c r="C8" t="n">
         <v>418.9534745673844</v>
       </c>
+      <c r="D8" t="n">
+        <v>42.44409122825819</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7499102797000201</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11.04967838753878</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.159929495478906</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.258518386057117e+21</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.710199543222091e+21</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -520,6 +688,24 @@
       <c r="C9" t="n">
         <v>417.3128580357806</v>
       </c>
+      <c r="D9" t="n">
+        <v>42.44218488948731</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.7470544215682562</v>
+      </c>
+      <c r="F9" t="n">
+        <v>11.04878331212081</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.155220601578615</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.254034384082513e+21</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.700298595362045e+21</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -531,6 +717,24 @@
       <c r="C10" t="n">
         <v>416.1932663666528</v>
       </c>
+      <c r="D10" t="n">
+        <v>42.4405035218423</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.745218554093428</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11.04691363989781</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.151774949612651</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.249866921559139e+21</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.692972593422775e+21</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -542,6 +746,24 @@
       <c r="C11" t="n">
         <v>415.6648369455991</v>
       </c>
+      <c r="D11" t="n">
+        <v>42.43907546692949</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.7445327309176301</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11.04402116558381</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.149778072873479</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.246068026676987e+21</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.688540698716829e+21</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -553,6 +775,24 @@
       <c r="C12" t="n">
         <v>415.7998370012074</v>
       </c>
+      <c r="D12" t="n">
+        <v>42.43793054450263</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.7451320476182962</v>
+      </c>
+      <c r="F12" t="n">
+        <v>11.04005530126748</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.14941617222689</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.242692293354877e+21</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.687335478104076e+21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -564,6 +804,24 @@
       <c r="C13" t="n">
         <v>416.5592133762611</v>
       </c>
+      <c r="D13" t="n">
+        <v>42.43701178886619</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7469356629167155</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11.03516009339121</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.150606055769755</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.239639247247439e+21</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.689086786565722e+21</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -575,6 +833,24 @@
       <c r="C14" t="n">
         <v>417.7298116094724</v>
       </c>
+      <c r="D14" t="n">
+        <v>42.43598663339942</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7494951912848835</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11.03009163236193</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.152896574019431</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.23631683055853e+21</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.692329074500623e+21</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -586,6 +862,24 @@
       <c r="C15" t="n">
         <v>419.3534310486251</v>
       </c>
+      <c r="D15" t="n">
+        <v>42.43485460746579</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7528858879023258</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11.02486495351779</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.156399337633289</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.23272820028474e+21</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.697224604226999e+21</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -597,6 +891,24 @@
       <c r="C16" t="n">
         <v>421.289869105273</v>
       </c>
+      <c r="D16" t="n">
+        <v>42.43378254228695</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7568904268907196</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11.01912438989453</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.160659981197088</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.229174533758087e+21</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.703500445040098e+21</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -608,6 +920,24 @@
       <c r="C17" t="n">
         <v>423.3956521760683</v>
       </c>
+      <c r="D17" t="n">
+        <v>42.43295038844736</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7612877017405973</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11.01249528374952</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.165209816330624</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.225980333155709e+21</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.710900549691027e+21</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -619,6 +949,24 @@
       <c r="C18" t="n">
         <v>425.5115544918795</v>
       </c>
+      <c r="D18" t="n">
+        <v>42.43273861752981</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7658541855736983</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11.00433066219765</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.169479145009298</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.22385900138616e+21</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.719471459566766e+21</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -630,6 +978,24 @@
       <c r="C19" t="n">
         <v>427.4925353906402</v>
       </c>
+      <c r="D19" t="n">
+        <v>42.43329622515405</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7703630076971821</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10.99430098093884</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.173007537596161</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.223071364735964e+21</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.728918511465416e+21</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -641,6 +1007,24 @@
       <c r="C20" t="n">
         <v>429.1998129530964</v>
       </c>
+      <c r="D20" t="n">
+        <v>42.43465097821929</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7745827054067158</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10.98224220432122</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.175375891322589</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.223643502285547e+21</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.738759471748986e+21</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -652,6 +1036,24 @@
       <c r="C21" t="n">
         <v>430.4914143824956</v>
       </c>
+      <c r="D21" t="n">
+        <v>42.43683498388354</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7782754581680008</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10.96798505960578</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.176160204700194</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.225612214311102e+21</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.748504465999978e+21</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -663,6 +1065,24 @@
       <c r="C22" t="n">
         <v>431.2211502223228</v>
       </c>
+      <c r="D22" t="n">
+        <v>42.43988597440615</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.7811946988171805</v>
+      </c>
+      <c r="F22" t="n">
+        <v>10.95135245897768</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.174933692961485</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.229027522036664e+21</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.757649442926939e+21</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -674,6 +1094,24 @@
       <c r="C23" t="n">
         <v>431.2372821999722</v>
       </c>
+      <c r="D23" t="n">
+        <v>42.44384886313545</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.7830820421603265</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10.93215773484724</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.171255102867324</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.23395604756657e+21</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.765667964006252e+21</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -685,6 +1123,24 @@
       <c r="C24" t="n">
         <v>430.2551618905309</v>
       </c>
+      <c r="D24" t="n">
+        <v>42.44867793373786</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7834136504995379</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10.91041626914134</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.164373895145711</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.240305754256194e+21</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.771296275251311e+21</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -696,6 +1152,24 @@
       <c r="C25" t="n">
         <v>428.0800376313587</v>
       </c>
+      <c r="D25" t="n">
+        <v>42.45362154627175</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7816739152715855</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10.88765194396727</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.154085999329971</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.24671086852155e+21</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.77226900606393e+21</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -707,6 +1181,24 @@
       <c r="C26" t="n">
         <v>425.6033677529034</v>
       </c>
+      <c r="D26" t="n">
+        <v>42.45791939356296</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7793304322547477</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10.86536566796476</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.143115071458702</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.251768997912987e+21</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.770790459595955e+21</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -718,6 +1210,24 @@
       <c r="C27" t="n">
         <v>422.936867142097</v>
       </c>
+      <c r="D27" t="n">
+        <v>42.46143227252033</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7765685713949889</v>
+      </c>
+      <c r="F27" t="n">
+        <v>10.84370784685022</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.131799684930566</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.255188876992636e+21</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.767056190376915e+21</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -729,6 +1239,24 @@
       <c r="C28" t="n">
         <v>420.1755375981427</v>
       </c>
+      <c r="D28" t="n">
+        <v>42.46403000270796</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7735479790534373</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10.8228005628292</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.120416881753002</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.256695422969313e+21</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.761225566867821e+21</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -740,6 +1268,24 @@
       <c r="C29" t="n">
         <v>417.417853342253</v>
       </c>
+      <c r="D29" t="n">
+        <v>42.46557728361371</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7704364888399964</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10.80276794881121</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.109255096204137</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.256006337418378e+21</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.753478769585069e+21</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -751,6 +1297,24 @@
       <c r="C30" t="n">
         <v>414.7663945045842</v>
       </c>
+      <c r="D30" t="n">
+        <v>42.46593263208331</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7674111451893776</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10.7837369598319</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.098605809467424</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.252832381022518e+21</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.744016215117948e+21</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -762,6 +1326,24 @@
       <c r="C31" t="n">
         <v>412.3286128362421</v>
       </c>
+      <c r="D31" t="n">
+        <v>42.46494716528444</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7646594026160226</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10.76583946337139</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.088776499228255</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.24687809674967e+21</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.733058003312376e+21</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -773,6 +1355,24 @@
       <c r="C32" t="n">
         <v>410.2052331317847</v>
       </c>
+      <c r="D32" t="n">
+        <v>42.46265046295588</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.762380582090916</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10.748977313057</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.080001025928615</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.23821247630089e+21</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.721124753956329e+21</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -784,6 +1384,24 @@
       <c r="C33" t="n">
         <v>408.4183355209385</v>
       </c>
+      <c r="D33" t="n">
+        <v>42.46035196123988</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7607878220202685</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10.73144555065918</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.072010180411905</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.229431667992308e+21</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.710683146026658e+21</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -795,6 +1413,24 @@
       <c r="C34" t="n">
         <v>407.0634450516507</v>
       </c>
+      <c r="D34" t="n">
+        <v>42.45838659209359</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7601093877741218</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10.71278827818192</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.064963604035343</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.221185922138149e+21</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.702722255614618e+21</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -806,6 +1442,24 @@
       <c r="C35" t="n">
         <v>406.1750346464005</v>
       </c>
+      <c r="D35" t="n">
+        <v>42.45675005318579</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7604142053990873</v>
+      </c>
+      <c r="F35" t="n">
+        <v>10.69303267582836</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.058943360135769</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.213464415812678e+21</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.697363451505426e+21</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -817,6 +1471,24 @@
       <c r="C36" t="n">
         <v>405.3092870830217</v>
       </c>
+      <c r="D36" t="n">
+        <v>42.45504636706889</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7607962662918791</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10.67299027539107</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.052936904453107</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.205554850594021e+21</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.692026646178183e+21</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -828,6 +1500,24 @@
       <c r="C37" t="n">
         <v>404.2438914323631</v>
       </c>
+      <c r="D37" t="n">
+        <v>42.45331447459918</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7608453544402783</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10.65258849224799</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.046354925901311</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.197529674951275e+21</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.685856034634698e+21</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -839,6 +1529,24 @@
       <c r="C38" t="n">
         <v>402.8826237019493</v>
       </c>
+      <c r="D38" t="n">
+        <v>42.45164043685785</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.76039401972414</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10.63166368281809</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.038924775757648</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.189544631825892e+21</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.678608702003438e+21</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -850,6 +1558,24 @@
       <c r="C39" t="n">
         <v>401.3082047760989</v>
       </c>
+      <c r="D39" t="n">
+        <v>42.44998678934458</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7595865024987088</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10.6102990528876</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.030881959854856</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.181534206723933e+21</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.670564500457114e+21</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -861,6 +1587,24 @@
       <c r="C40" t="n">
         <v>399.6087932587516</v>
       </c>
+      <c r="D40" t="n">
+        <v>42.44831279281472</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.758578352722604</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10.58858249483566</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.022475478918441</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.173427808724873e+21</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.6620197138401e+21</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -872,6 +1616,24 @@
       <c r="C41" t="n">
         <v>397.8785953554484</v>
       </c>
+      <c r="D41" t="n">
+        <v>42.44657400419414</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7575378153873329</v>
+      </c>
+      <c r="F41" t="n">
+        <v>10.566606444147</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.013968518420821</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.165148961355415e+21</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.653289101156052e+21</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -883,6 +1645,24 @@
       <c r="C42" t="n">
         <v>396.2184937246928</v>
       </c>
+      <c r="D42" t="n">
+        <v>42.44472184565777</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7566472521262007</v>
+      </c>
+      <c r="F42" t="n">
+        <v>10.54446945951813</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.005634152316716</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.156614891639442e+21</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.644707883145052e+21</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -894,6 +1674,24 @@
       <c r="C43" t="n">
         <v>394.7366909270571</v>
       </c>
+      <c r="D43" t="n">
+        <v>42.44270317966924</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7561045835358349</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10.52227592716351</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.9977671574004109</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.147735803930797e+21</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.63663356649768e+21</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -905,6 +1703,24 @@
       <c r="C44" t="n">
         <v>393.5493611149967</v>
       </c>
+      <c r="D44" t="n">
+        <v>42.44045990061392</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.7561247302520123</v>
+      </c>
+      <c r="F44" t="n">
+        <v>10.50013659641092</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.9906701383777949</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.138414428560545e+21</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.629446833886596e+21</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -916,6 +1732,24 @@
       <c r="C45" t="n">
         <v>392.7813012795793</v>
       </c>
+      <c r="D45" t="n">
+        <v>42.43792855695828</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.7569410232650402</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10.47816923779082</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.9846727655535434</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.128545741024548e+21</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.623552748851356e+21</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -927,6 +1761,24 @@
       <c r="C46" t="n">
         <v>392.5680525264239</v>
       </c>
+      <c r="D46" t="n">
+        <v>42.43504126274884</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.7588096544075755</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10.45649665765207</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.9801194127018964</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2.11801897068632e+21</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.619388575238321e+21</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -938,6 +1790,24 @@
       <c r="C47" t="n">
         <v>393.0643532283962</v>
       </c>
+      <c r="D47" t="n">
+        <v>42.43173204534736</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.7620274527909917</v>
+      </c>
+      <c r="F47" t="n">
+        <v>10.43523444015454</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.97740256112232</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2.106729023142132e+21</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.617466813348005e+21</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -949,6 +1819,24 @@
       <c r="C48" t="n">
         <v>394.0819221902975</v>
       </c>
+      <c r="D48" t="n">
+        <v>42.42808774305605</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.7662636852668115</v>
+      </c>
+      <c r="F48" t="n">
+        <v>10.4141594551151</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.9759932949003458</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2.094826168771593e+21</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.617150286637939e+21</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -960,6 +1848,24 @@
       <c r="C49" t="n">
         <v>395.2344162494065</v>
       </c>
+      <c r="D49" t="n">
+        <v>42.42433258399214</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.7708249886415384</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10.39280141888988</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.9748324502140208</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.082694411420967e+21</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.617235183880852e+21</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -971,6 +1877,24 @@
       <c r="C50" t="n">
         <v>396.5108833113108</v>
       </c>
+      <c r="D50" t="n">
+        <v>42.42053026997947</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.7757035995282625</v>
+      </c>
+      <c r="F50" t="n">
+        <v>10.37107181908333</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.9738741486896754</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2.070452351838956e+21</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.617782411492344e+21</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -982,6 +1906,24 @@
       <c r="C51" t="n">
         <v>397.9013275045389</v>
       </c>
+      <c r="D51" t="n">
+        <v>42.41674817627388</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.7808942380712474</v>
+      </c>
+      <c r="F51" t="n">
+        <v>10.34888046056796</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.9730678820517576</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2.058222998376185e+21</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.618863728721204e+21</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -993,6 +1935,24 @@
       <c r="C52" t="n">
         <v>399.3949943167649</v>
       </c>
+      <c r="D52" t="n">
+        <v>42.41305857655149</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7863910592622296</v>
+      </c>
+      <c r="F52" t="n">
+        <v>10.32613295900856</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.9723682869080063</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2.046135527115557e+21</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.620557539190411e+21</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1004,6 +1964,24 @@
       <c r="C53" t="n">
         <v>400.9802835590224</v>
       </c>
+      <c r="D53" t="n">
+        <v>42.40953913449315</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.7921875785462027</v>
+      </c>
+      <c r="F53" t="n">
+        <v>10.30273073165005</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.9717204716938801</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.03432604144537e+21</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.622949586158581e+21</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1015,6 +1993,24 @@
       <c r="C54" t="n">
         <v>402.6446550841614</v>
       </c>
+      <c r="D54" t="n">
+        <v>42.40627343939636</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.7982765860282725</v>
+      </c>
+      <c r="F54" t="n">
+        <v>10.27857059800048</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.971068016506652</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.022938402591681e+21</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.626134268567114e+21</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1026,6 +2022,24 @@
       <c r="C55" t="n">
         <v>404.3745265485809</v>
       </c>
+      <c r="D55" t="n">
+        <v>42.40335159065177</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.804650047211281</v>
+      </c>
+      <c r="F55" t="n">
+        <v>10.25354462758253</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.9703522427825907</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2.01212528681603e+21</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.630215948066377e+21</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1037,6 +2051,24 @@
       <c r="C56" t="n">
         <v>406.155162432959</v>
       </c>
+      <c r="D56" t="n">
+        <v>42.40087083656191</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8112989877573382</v>
+      </c>
+      <c r="F56" t="n">
+        <v>10.22753991786946</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.9695073877941082</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2.002049441570728e+21</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.635310348218386e+21</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1048,6 +2080,24 @@
       <c r="C57" t="n">
         <v>407.9362937090632</v>
       </c>
+      <c r="D57" t="n">
+        <v>42.39890635144663</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8181384032206095</v>
+      </c>
+      <c r="F57" t="n">
+        <v>10.20048942444108</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.9683970924704691</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.992835541339045e+21</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.641355480733492e+21</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1059,6 +2109,24 @@
       <c r="C58" t="n">
         <v>409.2460907400736</v>
       </c>
+      <c r="D58" t="n">
+        <v>42.39717265886622</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8241570381922723</v>
+      </c>
+      <c r="F58" t="n">
+        <v>10.17294473758723</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.966011528224006</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.984011578350421e+21</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.645954963131053e+21</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1070,6 +2138,24 @@
       <c r="C59" t="n">
         <v>409.9459791083885</v>
       </c>
+      <c r="D59" t="n">
+        <v>42.39566202506546</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8290582969878664</v>
+      </c>
+      <c r="F59" t="n">
+        <v>10.14497372286063</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.9620547555234332</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.975569822558582e+21</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.648542311139578e+21</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1081,6 +2167,24 @@
       <c r="C60" t="n">
         <v>410.0578502501226</v>
       </c>
+      <c r="D60" t="n">
+        <v>42.39449217059983</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8328920347988124</v>
+      </c>
+      <c r="F60" t="n">
+        <v>10.11643751560939</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.956573518815757</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.967709576144235e+21</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.649417275894404e+21</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1092,6 +2196,24 @@
       <c r="C61" t="n">
         <v>409.5902903510652</v>
       </c>
+      <c r="D61" t="n">
+        <v>42.3938041384685</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.8356855326287622</v>
+      </c>
+      <c r="F61" t="n">
+        <v>10.08716865483216</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.9495788201383462</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.960667135784816e+21</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.648864106054304e+21</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1103,6 +2225,24 @@
       <c r="C62" t="n">
         <v>408.5537229470084</v>
       </c>
+      <c r="D62" t="n">
+        <v>42.39375032005747</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.8374713041395283</v>
+      </c>
+      <c r="F62" t="n">
+        <v>10.05699180371452</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.9410814171274137</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.954696387458367e+21</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.647189181346158e+21</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1114,6 +2254,24 @@
       <c r="C63" t="n">
         <v>406.9693330335306</v>
       </c>
+      <c r="D63" t="n">
+        <v>42.39436263292714</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.838288155081259</v>
+      </c>
+      <c r="F63" t="n">
+        <v>10.02585499497521</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.9311454927921343</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.949838122588723e+21</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.644527143950587e+21</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1125,6 +2283,24 @@
       <c r="C64" t="n">
         <v>404.8628525891687</v>
       </c>
+      <c r="D64" t="n">
+        <v>42.39565236700517</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.8381818014432747</v>
+      </c>
+      <c r="F64" t="n">
+        <v>9.993725540828853</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.919845833631566</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.946097885677075e+21</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.640989299951826e+21</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1136,6 +2312,24 @@
       <c r="C65" t="n">
         <v>402.2600209715894</v>
       </c>
+      <c r="D65" t="n">
+        <v>42.39768646596502</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.8372055928141721</v>
+      </c>
+      <c r="F65" t="n">
+        <v>9.960514845485122</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.907250536633086</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.943580117652007e+21</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1.636777924558957e+21</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1147,6 +2341,24 @@
       <c r="C66" t="n">
         <v>399.1898850688965</v>
       </c>
+      <c r="D66" t="n">
+        <v>42.400541052215</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.8354213456972368</v>
+      </c>
+      <c r="F66" t="n">
+        <v>9.926125439250656</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.8934309891826409</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.942406625862665e+21</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1.632118965891523e+21</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1158,6 +2370,24 @@
       <c r="C67" t="n">
         <v>395.6851175800762</v>
       </c>
+      <c r="D67" t="n">
+        <v>42.40430281303313</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.8329003755131502</v>
+      </c>
+      <c r="F67" t="n">
+        <v>9.890451375433422</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.8784652097330433</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.94272002050129e+21</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1.627266570163303e+21</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1169,6 +2399,24 @@
       <c r="C68" t="n">
         <v>391.756537483491</v>
       </c>
+      <c r="D68" t="n">
+        <v>42.40904684011183</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.8296650815694432</v>
+      </c>
+      <c r="F68" t="n">
+        <v>9.853412171291371</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.8623878798231691</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1.944648254976616e+21</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.622359102353948e+21</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1180,6 +2428,24 @@
       <c r="C69" t="n">
         <v>386.8470909423675</v>
       </c>
+      <c r="D69" t="n">
+        <v>42.41433174838888</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.8244207391055763</v>
+      </c>
+      <c r="F69" t="n">
+        <v>9.815699141417269</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.8441488601404169</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1.947470345756139e+21</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1.614246801540317e+21</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1191,6 +2457,24 @@
       <c r="C70" t="n">
         <v>380.7130846233845</v>
       </c>
+      <c r="D70" t="n">
+        <v>42.42000549608444</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.8165744370468085</v>
+      </c>
+      <c r="F70" t="n">
+        <v>9.777543223742351</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.823327072739933</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.950937859931775e+21</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1.601533966634482e+21</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1202,6 +2486,24 @@
       <c r="C71" t="n">
         <v>374.690663696711</v>
       </c>
+      <c r="D71" t="n">
+        <v>42.42507373056798</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.8087619002724724</v>
+      </c>
+      <c r="F71" t="n">
+        <v>9.740368491992736</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.8031358951403983</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1.953395512335908e+21</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.588021088752726e+21</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1213,6 +2515,24 @@
       <c r="C72" t="n">
         <v>369.9423232635739</v>
       </c>
+      <c r="D72" t="n">
+        <v>42.42866515263942</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.8033480519567651</v>
+      </c>
+      <c r="F72" t="n">
+        <v>9.705338148084934</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.7862573449180287</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.953373108893762e+21</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1.577197501799005e+21</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1224,6 +2544,24 @@
       <c r="C73" t="n">
         <v>366.4133017357839</v>
       </c>
+      <c r="D73" t="n">
+        <v>42.43088558018941</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.8002958468834436</v>
+      </c>
+      <c r="F73" t="n">
+        <v>9.672183962199092</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.7724461908803761</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1.951027544541872e+21</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1.569154441398711e+21</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1235,6 +2573,24 @@
       <c r="C74" t="n">
         <v>364.0341357929535</v>
       </c>
+      <c r="D74" t="n">
+        <v>42.43187242755521</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.7995354506061134</v>
+      </c>
+      <c r="F74" t="n">
+        <v>9.640606411985397</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.7614318798003219</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1.946577897074915e+21</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.563933370796664e+21</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1246,6 +2602,24 @@
       <c r="C75" t="n">
         <v>362.7202600317686</v>
       </c>
+      <c r="D75" t="n">
+        <v>42.43179725403376</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.8009640112022098</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.610272575806931</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.7529173527181464</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1.940307191529739e+21</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1.561533015049635e+21</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1257,6 +2631,24 @@
       <c r="C76" t="n">
         <v>362.3716105520215</v>
       </c>
+      <c r="D76" t="n">
+        <v>42.43086873781054</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.8044457713411962</v>
+      </c>
+      <c r="F76" t="n">
+        <v>9.580812893640985</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.7465750099738369</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1.932564052267176e+21</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1.561919673681683e+21</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1268,6 +2660,24 @@
       <c r="C77" t="n">
         <v>362.8704389055214</v>
       </c>
+      <c r="D77" t="n">
+        <v>42.42936812297764</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.8098123337931799</v>
+      </c>
+      <c r="F77" t="n">
+        <v>9.551792337493032</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.7420370112107139</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1.923821178751342e+21</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1.565086258054092e+21</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1279,6 +2689,24 @@
       <c r="C78" t="n">
         <v>364.0650531567343</v>
       </c>
+      <c r="D78" t="n">
+        <v>42.4279429150512</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.8168628773722287</v>
+      </c>
+      <c r="F78" t="n">
+        <v>9.522475088238208</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.7388147617465255</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1.915184925156129e+21</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1.571484346515056e+21</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1290,6 +2718,24 @@
       <c r="C79" t="n">
         <v>365.7815741762672</v>
       </c>
+      <c r="D79" t="n">
+        <v>42.42710178493682</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.8253293567743839</v>
+      </c>
+      <c r="F79" t="n">
+        <v>9.492250114222708</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.7364044895319836</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1.907500868479059e+21</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1.581256246474181e+21</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1301,6 +2747,24 @@
       <c r="C80" t="n">
         <v>367.1273761911473</v>
       </c>
+      <c r="D80" t="n">
+        <v>42.42665163282906</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.8331740277715979</v>
+      </c>
+      <c r="F80" t="n">
+        <v>9.461394750563564</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.7330480000218245</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1.900444693442791e+21</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1.590232535536663e+21</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1312,6 +2776,24 @@
       <c r="C81" t="n">
         <v>367.3143474899389</v>
       </c>
+      <c r="D81" t="n">
+        <v>42.42658743021821</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.8385878174739336</v>
+      </c>
+      <c r="F81" t="n">
+        <v>9.429937051222309</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.7272049182851223</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1.894004399788176e+21</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1.594990688306808e+21</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1323,6 +2805,24 @@
       <c r="C82" t="n">
         <v>366.698843314406</v>
       </c>
+      <c r="D82" t="n">
+        <v>42.42654508762703</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.842273325446888</v>
+      </c>
+      <c r="F82" t="n">
+        <v>9.398348323821697</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.71972455111072</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1.887579872005836e+21</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1.596415959697456e+21</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1334,6 +2834,24 @@
       <c r="C83" t="n">
         <v>366.1512833745776</v>
       </c>
+      <c r="D83" t="n">
+        <v>42.42570452427341</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.8460469055813509</v>
+      </c>
+      <c r="F83" t="n">
+        <v>9.367627797495468</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.7125402473334496</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1.879829130765909e+21</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1.596838351403557e+21</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1345,6 +2863,24 @@
       <c r="C84" t="n">
         <v>365.6886421494929</v>
       </c>
+      <c r="D84" t="n">
+        <v>42.42395168279472</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.8499303168307386</v>
+      </c>
+      <c r="F84" t="n">
+        <v>9.337870452809792</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.7057015683586703</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1.870575939407352e+21</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1.596131873275596e+21</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1356,6 +2892,24 @@
       <c r="C85" t="n">
         <v>365.3271883980977</v>
       </c>
+      <c r="D85" t="n">
+        <v>42.42116077597082</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.8539421588692874</v>
+      </c>
+      <c r="F85" t="n">
+        <v>9.309178086950107</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.6992575931217224</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1.859630936593832e+21</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1.594148977425232e+21</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1367,6 +2921,24 @@
       <c r="C86" t="n">
         <v>365.0850197957042</v>
       </c>
+      <c r="D86" t="n">
+        <v>42.41719087622305</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.8581030015604028</v>
+      </c>
+      <c r="F86" t="n">
+        <v>9.281663750827246</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.6932625436768634</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1.846788448492751e+21</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1.590726703512989e+21</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1378,6 +2950,24 @@
       <c r="C87" t="n">
         <v>364.98222660146</v>
       </c>
+      <c r="D87" t="n">
+        <v>42.41188444596704</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.8624354638964282</v>
+      </c>
+      <c r="F87" t="n">
+        <v>9.25545267851186</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.6877766670586141</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1.831826888999259e+21</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1.585686079547123e+21</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1389,6 +2979,24 @@
       <c r="C88" t="n">
         <v>365.0410595539349</v>
       </c>
+      <c r="D88" t="n">
+        <v>42.40506581982487</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.8669642551362809</v>
+      </c>
+      <c r="F88" t="n">
+        <v>9.230683313564917</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.6828662706339353</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1.814509827434369e+21</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1.578831834159935e+21</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1400,6 +3008,24 @@
       <c r="C89" t="n">
         <v>365.2860989827072</v>
       </c>
+      <c r="D89" t="n">
+        <v>42.39653966837782</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.8717161632017238</v>
+      </c>
+      <c r="F89" t="n">
+        <v>9.207509429396948</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.6786052218863692</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1.79458810586124e+21</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1.56995276246526e+21</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1411,6 +3037,24 @@
       <c r="C90" t="n">
         <v>365.7358411269458</v>
       </c>
+      <c r="D90" t="n">
+        <v>42.3860805433244</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.8766975760515593</v>
+      </c>
+      <c r="F90" t="n">
+        <v>9.186111061767221</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.6750614048207326</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1.77178884973709e+21</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1.558770455155281e+21</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1422,6 +3066,24 @@
       <c r="C91" t="n">
         <v>364.9444444365689</v>
       </c>
+      <c r="D91" t="n">
+        <v>42.37190535897146</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.8780714468282137</v>
+      </c>
+      <c r="F91" t="n">
+        <v>9.168378691818971</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.6699676288136168</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1.7434785604722e+21</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1.536190857572743e+21</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1433,6 +3095,24 @@
       <c r="C92" t="n">
         <v>361.836925248409</v>
       </c>
+      <c r="D92" t="n">
+        <v>42.35257456627382</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.872922735510096</v>
+      </c>
+      <c r="F92" t="n">
+        <v>9.155768676906726</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.6616948000941381</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1.707747361660757e+21</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1.49583186439946e+21</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1444,6 +3124,24 @@
       <c r="C93" t="n">
         <v>356.8831909871107</v>
       </c>
+      <c r="D93" t="n">
+        <v>42.32819402060652</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.8623222617716311</v>
+      </c>
+      <c r="F93" t="n">
+        <v>9.148399658853563</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.6511531246623151</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1.665273626604646e+21</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1.440885941354629e+21</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1455,6 +3153,24 @@
       <c r="C94" t="n">
         <v>350.8802797836808</v>
       </c>
+      <c r="D94" t="n">
+        <v>42.29917223518919</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.8481920174288757</v>
+      </c>
+      <c r="F94" t="n">
+        <v>9.146327928703311</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.6397903800968792</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1.617272649785198e+21</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1.376414731547678e+21</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1466,6 +3182,24 @@
       <c r="C95" t="n">
         <v>343.9364680572268</v>
       </c>
+      <c r="D95" t="n">
+        <v>42.26528928864261</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.8307998191584939</v>
+      </c>
+      <c r="F95" t="n">
+        <v>9.149755062961749</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.6277940279274333</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1.563978452421858e+21</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1.303776669425569e+21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -1477,6 +3211,24 @@
       <c r="C96" t="n">
         <v>336.1786518066829</v>
       </c>
+      <c r="D96" t="n">
+        <v>42.22636884884817</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.8104896139032179</v>
+      </c>
+      <c r="F96" t="n">
+        <v>9.158867703681134</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.6153601181938069</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1.505775236768725e+21</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1.224601329071087e+21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -1488,6 +3240,24 @@
       <c r="C97" t="n">
         <v>327.7614211654175</v>
       </c>
+      <c r="D97" t="n">
+        <v>42.18229045088326</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.7876999163413686</v>
+      </c>
+      <c r="F97" t="n">
+        <v>9.173836613868502</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.6027121257868805</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1.443199470616108e+21</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1.140755401795755e+21</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -1499,6 +3269,24 @@
       <c r="C98" t="n">
         <v>318.8642161859688</v>
       </c>
+      <c r="D98" t="n">
+        <v>42.13298893474061</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.7629505916259512</v>
+      </c>
+      <c r="F98" t="n">
+        <v>9.194819081342255</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.5901029388426847</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1.376915129017091e+21</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1.054228296144604e+21</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -1510,6 +3298,24 @@
       <c r="C99" t="n">
         <v>309.6874947408068</v>
       </c>
+      <c r="D99" t="n">
+        <v>42.07845112273151</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.7368252854999224</v>
+      </c>
+      <c r="F99" t="n">
+        <v>9.221962829711707</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.5778149496340537</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1.307681199691972e+21</v>
+      </c>
+      <c r="I99" t="n">
+        <v>9.670099776708082e+20</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -1521,6 +3327,24 @@
       <c r="C100" t="n">
         <v>300.4482367496789</v>
       </c>
+      <c r="D100" t="n">
+        <v>42.01870998425089</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.7099509803913434</v>
+      </c>
+      <c r="F100" t="n">
+        <v>9.255409619553664</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.5661609144699786</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1.23631434962583e+21</v>
+      </c>
+      <c r="I100" t="n">
+        <v>8.809746197049935e+20</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -1531,6 +3355,24 @@
       </c>
       <c r="C101" t="n">
         <v>291.3751740542384</v>
+      </c>
+      <c r="D101" t="n">
+        <v>41.95383668895239</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.6829764053424003</v>
+      </c>
+      <c r="F101" t="n">
+        <v>9.295301295974026</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.5554849719302345</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1.163650667869686e+21</v>
+      </c>
+      <c r="I101" t="n">
+        <v>7.977824673819062e+20</v>
       </c>
     </row>
   </sheetData>

--- a/results/radial_T_right.xlsx
+++ b/results/radial_T_right.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,2954 +413,3259 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Radius_mm</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>T_K</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>T_err</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Intercept_b</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Intercept_b_err</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Partition_func</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Partition_func_err</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Electron_concentration</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Electron_concentration_err</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Electron_concentration_rel_err</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5975.0224335999</v>
+        <v>5111.512098784055</v>
       </c>
       <c r="C2" t="n">
-        <v>436.0153424180646</v>
+        <v>227.2326710687479</v>
       </c>
       <c r="D2" t="n">
-        <v>42.45879900056699</v>
+        <v>40.91051943543837</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7816433797668262</v>
+        <v>0.5566189020135847</v>
       </c>
       <c r="F2" t="n">
-        <v>11.03705204749668</v>
+        <v>9.084994330131085</v>
       </c>
       <c r="G2" t="n">
-        <v>1.204715881985064</v>
+        <v>0.4064263878113362</v>
       </c>
       <c r="H2" t="n">
-        <v>2.289362620998454e+21</v>
+        <v>4.00660829820412e+20</v>
       </c>
       <c r="I2" t="n">
-        <v>1.806828629959155e+21</v>
+        <v>2.237345151623182e+20</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5584137467658185</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.02097979797979798</v>
+        <v>0.0382020202020202</v>
       </c>
       <c r="B3" t="n">
-        <v>5976.483440810643</v>
+        <v>5114.778007842215</v>
       </c>
       <c r="C3" t="n">
-        <v>432.6340136305364</v>
+        <v>234.7534011086701</v>
       </c>
       <c r="D3" t="n">
-        <v>42.45608161327682</v>
+        <v>40.90313651591293</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7752025318951238</v>
+        <v>0.5743072220386195</v>
       </c>
       <c r="F3" t="n">
-        <v>11.04109028165649</v>
+        <v>9.090841108748434</v>
       </c>
       <c r="G3" t="n">
-        <v>1.196151733866501</v>
+        <v>0.4206603347545618</v>
       </c>
       <c r="H3" t="n">
-        <v>2.283985339416603e+21</v>
+        <v>3.979696301936834e+20</v>
       </c>
       <c r="I3" t="n">
-        <v>1.787757680859141e+21</v>
+        <v>2.292975074879464e+20</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5761683558023063</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04195959595959596</v>
+        <v>0.0764040404040404</v>
       </c>
       <c r="B4" t="n">
-        <v>5977.683350030858</v>
+        <v>5116.972391028158</v>
       </c>
       <c r="C4" t="n">
-        <v>429.3835875150403</v>
+        <v>239.0764860084821</v>
       </c>
       <c r="D4" t="n">
-        <v>42.45343879200961</v>
+        <v>40.89814962957688</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7690695055593569</v>
+        <v>0.5843817967481472</v>
       </c>
       <c r="F4" t="n">
-        <v>11.04440867401985</v>
+        <v>9.094775661256559</v>
       </c>
       <c r="G4" t="n">
-        <v>1.187799747817352</v>
+        <v>0.4289427346290487</v>
       </c>
       <c r="H4" t="n">
-        <v>2.278641782127393e+21</v>
+        <v>3.961613272628239e+20</v>
       </c>
       <c r="I4" t="n">
-        <v>1.769485863616299e+21</v>
+        <v>2.322622248233802e+20</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5862819231451416</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.06293939393939393</v>
+        <v>0.1146060606060606</v>
       </c>
       <c r="B5" t="n">
-        <v>5978.60825841264</v>
+        <v>5118.302302225932</v>
       </c>
       <c r="C5" t="n">
-        <v>426.3266121480419</v>
+        <v>241.2501525484604</v>
       </c>
       <c r="D5" t="n">
-        <v>42.45089408496061</v>
+        <v>40.89492343591213</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7633579107055515</v>
+        <v>0.5893885485056568</v>
       </c>
       <c r="F5" t="n">
-        <v>11.04696777742271</v>
+        <v>9.097162738966963</v>
       </c>
       <c r="G5" t="n">
-        <v>1.179828270898243</v>
+        <v>0.4331703910703774</v>
       </c>
       <c r="H5" t="n">
-        <v>2.273377320723783e+21</v>
+        <v>3.949889378960547e+20</v>
       </c>
       <c r="I5" t="n">
-        <v>1.752303214846213e+21</v>
+        <v>2.335604503972221e+20</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5913088392837116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.08391919191919192</v>
+        <v>0.1528080808080808</v>
       </c>
       <c r="B6" t="n">
-        <v>5979.243865526048</v>
+        <v>5120.509819030264</v>
       </c>
       <c r="C6" t="n">
-        <v>423.5263182420726</v>
+        <v>236.9746738618033</v>
       </c>
       <c r="D6" t="n">
-        <v>42.44847146165682</v>
+        <v>40.89057313058744</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7581826336094584</v>
+        <v>0.5784442264033425</v>
       </c>
       <c r="F6" t="n">
-        <v>11.04872698902483</v>
+        <v>9.101128897867858</v>
       </c>
       <c r="G6" t="n">
-        <v>1.172410286608973</v>
+        <v>0.4260283978880937</v>
       </c>
       <c r="H6" t="n">
-        <v>2.26823760543373e+21</v>
+        <v>3.934458064102661e+20</v>
       </c>
       <c r="I6" t="n">
-        <v>1.736499680754814e+21</v>
+        <v>2.283304513108206e+20</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5803352014196556</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1048989898989899</v>
+        <v>0.191010101010101</v>
       </c>
       <c r="B7" t="n">
-        <v>5979.575396575801</v>
+        <v>5118.512172802089</v>
       </c>
       <c r="C7" t="n">
-        <v>421.0468458977961</v>
+        <v>230.1720394332137</v>
       </c>
       <c r="D7" t="n">
-        <v>42.44619543974098</v>
+        <v>40.89632951059612</v>
       </c>
       <c r="E7" t="n">
-        <v>0.753660386530566</v>
+        <v>0.5622779435656874</v>
       </c>
       <c r="F7" t="n">
-        <v>11.049644842682</v>
+        <v>9.097539609017202</v>
       </c>
       <c r="G7" t="n">
-        <v>1.165718977337093</v>
+        <v>0.413328720218574</v>
       </c>
       <c r="H7" t="n">
-        <v>2.263268919013235e+21</v>
+        <v>3.955610987937652e+20</v>
       </c>
       <c r="I7" t="n">
-        <v>1.722366791270159e+21</v>
+        <v>2.23140165409447e+20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5641104903639329</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.1258787878787879</v>
+        <v>0.2292121212121212</v>
       </c>
       <c r="B8" t="n">
-        <v>5979.587513062448</v>
+        <v>5109.014288572903</v>
       </c>
       <c r="C8" t="n">
-        <v>418.9534745673844</v>
+        <v>226.825711786905</v>
       </c>
       <c r="D8" t="n">
-        <v>42.44409122825819</v>
+        <v>40.91510710143135</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7499102797000201</v>
+        <v>0.5561654557987701</v>
       </c>
       <c r="F8" t="n">
-        <v>11.04967838753878</v>
+        <v>9.080529829107034</v>
       </c>
       <c r="G8" t="n">
-        <v>1.159929495478906</v>
+        <v>0.4051208302384636</v>
       </c>
       <c r="H8" t="n">
-        <v>2.258518386057117e+21</v>
+        <v>4.023053546082549e+20</v>
       </c>
       <c r="I8" t="n">
-        <v>1.710199543222091e+21</v>
+        <v>2.244670805601328e+20</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5579520083164384</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1468585858585859</v>
+        <v>0.2674141414141414</v>
       </c>
       <c r="B9" t="n">
-        <v>5979.264209569993</v>
+        <v>5096.839082491528</v>
       </c>
       <c r="C9" t="n">
-        <v>417.3128580357806</v>
+        <v>223.0002413498386</v>
       </c>
       <c r="D9" t="n">
-        <v>42.44218488948731</v>
+        <v>40.9346835553772</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7470544215682562</v>
+        <v>0.5494010075193849</v>
       </c>
       <c r="F9" t="n">
-        <v>11.04878331212081</v>
+        <v>9.058859911855803</v>
       </c>
       <c r="G9" t="n">
-        <v>1.155220601578615</v>
+        <v>0.3955248258125769</v>
       </c>
       <c r="H9" t="n">
-        <v>2.254034384082513e+21</v>
+        <v>4.092796139958693e+20</v>
       </c>
       <c r="I9" t="n">
-        <v>1.700298595362045e+21</v>
+        <v>2.255675845190256e+20</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5511332028408874</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1678383838383838</v>
+        <v>0.3056161616161616</v>
       </c>
       <c r="B10" t="n">
-        <v>5978.588695040206</v>
+        <v>5090.667625294198</v>
       </c>
       <c r="C10" t="n">
-        <v>416.1932663666528</v>
+        <v>223.2437185314866</v>
       </c>
       <c r="D10" t="n">
-        <v>42.4405035218423</v>
+        <v>40.93816435049237</v>
       </c>
       <c r="E10" t="n">
-        <v>0.745218554093428</v>
+        <v>0.5513352063674489</v>
       </c>
       <c r="F10" t="n">
-        <v>11.04691363989781</v>
+        <v>9.04793327910191</v>
       </c>
       <c r="G10" t="n">
-        <v>1.151774949612651</v>
+        <v>0.3945578164805084</v>
       </c>
       <c r="H10" t="n">
-        <v>2.249866921559139e+21</v>
+        <v>4.102113277580748e+20</v>
       </c>
       <c r="I10" t="n">
-        <v>1.692972593422775e+21</v>
+        <v>2.268702756766801e+20</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5530570716235281</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1888181818181818</v>
+        <v>0.3438181818181818</v>
       </c>
       <c r="B11" t="n">
-        <v>5977.543256527786</v>
+        <v>5091.492970986809</v>
       </c>
       <c r="C11" t="n">
-        <v>415.6648369455991</v>
+        <v>232.1969266070167</v>
       </c>
       <c r="D11" t="n">
-        <v>42.43907546692949</v>
+        <v>40.92798981976597</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7445327309176301</v>
+        <v>0.5732606514991768</v>
       </c>
       <c r="F11" t="n">
-        <v>11.04402116558381</v>
+        <v>9.049392343088005</v>
       </c>
       <c r="G11" t="n">
-        <v>1.149778072873479</v>
+        <v>0.4105759738027671</v>
       </c>
       <c r="H11" t="n">
-        <v>2.246068026676987e+21</v>
+        <v>4.061242617117334e+20</v>
       </c>
       <c r="I11" t="n">
-        <v>1.688540698716829e+21</v>
+        <v>2.335430842607239e+20</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5750532688600922</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.2097979797979798</v>
+        <v>0.382020202020202</v>
       </c>
       <c r="B12" t="n">
-        <v>5976.109103007231</v>
+        <v>5095.139296963849</v>
       </c>
       <c r="C12" t="n">
-        <v>415.7998370012074</v>
+        <v>243.4857596610406</v>
       </c>
       <c r="D12" t="n">
-        <v>42.43793054450263</v>
+        <v>40.91232403728702</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7451320476182962</v>
+        <v>0.600271060017891</v>
       </c>
       <c r="F12" t="n">
-        <v>11.04005530126748</v>
+        <v>9.055846543894653</v>
       </c>
       <c r="G12" t="n">
-        <v>1.14941617222689</v>
+        <v>0.4314386157331216</v>
       </c>
       <c r="H12" t="n">
-        <v>2.242692293354877e+21</v>
+        <v>4.00096736313478e+20</v>
       </c>
       <c r="I12" t="n">
-        <v>1.687335478104076e+21</v>
+        <v>2.409217324090709e+20</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6021587044896749</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.2307777777777778</v>
+        <v>0.4202222222222222</v>
       </c>
       <c r="B13" t="n">
-        <v>5974.337541093772</v>
+        <v>5094.987315232336</v>
       </c>
       <c r="C13" t="n">
-        <v>416.5592133762611</v>
+        <v>247.7781210376418</v>
       </c>
       <c r="D13" t="n">
-        <v>42.43701178886619</v>
+        <v>40.90320916064937</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7469356629167155</v>
+        <v>0.6108895611590309</v>
       </c>
       <c r="F13" t="n">
-        <v>11.03516009339121</v>
+        <v>9.05557720077547</v>
       </c>
       <c r="G13" t="n">
-        <v>1.150606055769755</v>
+        <v>0.4390061186799801</v>
       </c>
       <c r="H13" t="n">
-        <v>2.239639247247439e+21</v>
+        <v>3.964546818636138e+20</v>
       </c>
       <c r="I13" t="n">
-        <v>1.689086786565722e+21</v>
+        <v>2.429514523837965e+20</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6128101482917419</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2517575757575757</v>
+        <v>0.4584242424242424</v>
       </c>
       <c r="B14" t="n">
-        <v>5972.501825190653</v>
+        <v>5092.830302420673</v>
       </c>
       <c r="C14" t="n">
-        <v>417.7298116094724</v>
+        <v>248.4086216391054</v>
       </c>
       <c r="D14" t="n">
-        <v>42.43598663339942</v>
+        <v>40.89808228182068</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7494951912848835</v>
+        <v>0.6129629394428942</v>
       </c>
       <c r="F14" t="n">
-        <v>11.03009163236193</v>
+        <v>9.051757895406263</v>
       </c>
       <c r="G14" t="n">
-        <v>1.152896574019431</v>
+        <v>0.4395790956375502</v>
       </c>
       <c r="H14" t="n">
-        <v>2.23631683055853e+21</v>
+        <v>3.942609534828148e+20</v>
       </c>
       <c r="I14" t="n">
-        <v>1.692329074500623e+21</v>
+        <v>2.424246179107696e+20</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6148836595895274</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2727373737373737</v>
+        <v>0.4966262626262626</v>
       </c>
       <c r="B15" t="n">
-        <v>5970.607242049798</v>
+        <v>5093.386745269504</v>
       </c>
       <c r="C15" t="n">
-        <v>419.3534310486251</v>
+        <v>242.1465095552552</v>
       </c>
       <c r="D15" t="n">
-        <v>42.43485460746579</v>
+        <v>40.8883710572229</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7528858879023258</v>
+        <v>0.5973802614580391</v>
       </c>
       <c r="F15" t="n">
-        <v>11.02486495351779</v>
+        <v>9.052742772067537</v>
       </c>
       <c r="G15" t="n">
-        <v>1.156399337633289</v>
+        <v>0.4286346123016731</v>
       </c>
       <c r="H15" t="n">
-        <v>2.23272820028474e+21</v>
+        <v>3.904932107344989e+20</v>
       </c>
       <c r="I15" t="n">
-        <v>1.697224604226999e+21</v>
+        <v>2.340045237925976e+20</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5992537574531613</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.2937171717171717</v>
+        <v>0.5348282828282829</v>
       </c>
       <c r="B16" t="n">
-        <v>5968.524530085347</v>
+        <v>5093.627011128893</v>
       </c>
       <c r="C16" t="n">
-        <v>421.289869105273</v>
+        <v>234.4274174912046</v>
       </c>
       <c r="D16" t="n">
-        <v>42.43378254228695</v>
+        <v>40.87918722873185</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7568904268907196</v>
+        <v>0.5782825486927907</v>
       </c>
       <c r="F16" t="n">
-        <v>11.01912438989453</v>
+        <v>9.053168105348046</v>
       </c>
       <c r="G16" t="n">
-        <v>1.160659981197088</v>
+        <v>0.415027892310145</v>
       </c>
       <c r="H16" t="n">
-        <v>2.229174533758087e+21</v>
+        <v>3.869415845664474e+20</v>
       </c>
       <c r="I16" t="n">
-        <v>1.703500445040098e+21</v>
+        <v>2.244635833041925e+20</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5800968214768</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.3146969696969697</v>
+        <v>0.573030303030303</v>
       </c>
       <c r="B17" t="n">
-        <v>5966.117075472211</v>
+        <v>5088.038844881178</v>
       </c>
       <c r="C17" t="n">
-        <v>423.3956521760683</v>
+        <v>234.0358406430693</v>
       </c>
       <c r="D17" t="n">
-        <v>42.43295038844736</v>
+        <v>40.87995887778297</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7612877017405973</v>
+        <v>0.5785854359162711</v>
       </c>
       <c r="F17" t="n">
-        <v>11.01249528374952</v>
+        <v>9.043290620479272</v>
       </c>
       <c r="G17" t="n">
-        <v>1.165209816330624</v>
+        <v>0.4130075901812891</v>
       </c>
       <c r="H17" t="n">
-        <v>2.225980333155709e+21</v>
+        <v>3.868177832887893e+20</v>
       </c>
       <c r="I17" t="n">
-        <v>1.710900549691027e+21</v>
+        <v>2.245032766290932e+20</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5803850968803164</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.3356767676767677</v>
+        <v>0.6112323232323232</v>
       </c>
       <c r="B18" t="n">
-        <v>5963.148368838366</v>
+        <v>5075.403920909971</v>
       </c>
       <c r="C18" t="n">
-        <v>425.5115544918795</v>
+        <v>239.2340718849036</v>
       </c>
       <c r="D18" t="n">
-        <v>42.43273861752981</v>
+        <v>40.89501163577347</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7658541855736983</v>
+        <v>0.5943849076522556</v>
       </c>
       <c r="F18" t="n">
-        <v>11.00433066219765</v>
+        <v>9.021074462340135</v>
       </c>
       <c r="G18" t="n">
-        <v>1.169479145009298</v>
+        <v>0.4191215059493626</v>
       </c>
       <c r="H18" t="n">
-        <v>2.22385900138616e+21</v>
+        <v>3.917198155721947e+20</v>
       </c>
       <c r="I18" t="n">
-        <v>1.719471459566766e+21</v>
+        <v>2.335425441333879e+20</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5961979324233231</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.3566565656565657</v>
+        <v>0.6494343434343435</v>
       </c>
       <c r="B19" t="n">
-        <v>5959.496091714745</v>
+        <v>5056.405353371365</v>
       </c>
       <c r="C19" t="n">
-        <v>427.4925353906402</v>
+        <v>241.5927970292925</v>
       </c>
       <c r="D19" t="n">
-        <v>42.43329622515405</v>
+        <v>40.92362259910688</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7703630076971821</v>
+        <v>0.6047643467776249</v>
       </c>
       <c r="F19" t="n">
-        <v>10.99430098093884</v>
+        <v>8.987972354128758</v>
       </c>
       <c r="G19" t="n">
-        <v>1.173007537596161</v>
+        <v>0.4186273076403418</v>
       </c>
       <c r="H19" t="n">
-        <v>2.223071364735964e+21</v>
+        <v>4.016100620024218e+20</v>
       </c>
       <c r="I19" t="n">
-        <v>1.728918511465416e+21</v>
+        <v>2.435986928702606e+20</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.606555253261537</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.3776363636363637</v>
+        <v>0.6876363636363636</v>
       </c>
       <c r="B20" t="n">
-        <v>5955.097076443844</v>
+        <v>5035.069088034627</v>
       </c>
       <c r="C20" t="n">
-        <v>429.1998129530964</v>
+        <v>234.7969207461148</v>
       </c>
       <c r="D20" t="n">
-        <v>42.43465097821929</v>
+        <v>40.9559278239268</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7745827054067158</v>
+        <v>0.5927444440187547</v>
       </c>
       <c r="F20" t="n">
-        <v>10.98224220432122</v>
+        <v>8.951229635210348</v>
       </c>
       <c r="G20" t="n">
-        <v>1.175375891322589</v>
+        <v>0.401828653272111</v>
       </c>
       <c r="H20" t="n">
-        <v>2.223643502285547e+21</v>
+        <v>4.131003251398641e+20</v>
       </c>
       <c r="I20" t="n">
-        <v>1.738759471748986e+21</v>
+        <v>2.455641405432669e+20</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5944418960699822</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.3986161616161616</v>
+        <v>0.7258383838383838</v>
       </c>
       <c r="B21" t="n">
-        <v>5949.884850093269</v>
+        <v>5020.257851919613</v>
       </c>
       <c r="C21" t="n">
-        <v>430.4914143824956</v>
+        <v>230.0245145122358</v>
       </c>
       <c r="D21" t="n">
-        <v>42.43683498388354</v>
+        <v>40.97314323699632</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7782754581680008</v>
+        <v>0.5841280175276057</v>
       </c>
       <c r="F21" t="n">
-        <v>10.96798505960578</v>
+        <v>8.925991443029796</v>
       </c>
       <c r="G21" t="n">
-        <v>1.176160204700194</v>
+        <v>0.3902617352676819</v>
       </c>
       <c r="H21" t="n">
-        <v>2.225612214311102e+21</v>
+        <v>4.190886152633643e+20</v>
       </c>
       <c r="I21" t="n">
-        <v>1.748504465999978e+21</v>
+        <v>2.454861958168915e+20</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5857620247274499</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.4195959595959596</v>
+        <v>0.7640404040404041</v>
       </c>
       <c r="B22" t="n">
-        <v>5943.788735121068</v>
+        <v>5018.547343570494</v>
       </c>
       <c r="C22" t="n">
-        <v>431.2211502223228</v>
+        <v>237.4919542915076</v>
       </c>
       <c r="D22" t="n">
-        <v>42.43988597440615</v>
+        <v>40.96052765786476</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7811946988171805</v>
+        <v>0.6035021382420503</v>
       </c>
       <c r="F22" t="n">
-        <v>10.95135245897768</v>
+        <v>8.923090863176544</v>
       </c>
       <c r="G22" t="n">
-        <v>1.174933692961485</v>
+        <v>0.4025266286519189</v>
       </c>
       <c r="H22" t="n">
-        <v>2.229027522036664e+21</v>
+        <v>4.137003001739995e+20</v>
       </c>
       <c r="I22" t="n">
-        <v>1.757649442926939e+21</v>
+        <v>2.503655304088307e+20</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.605185759603096</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.4405757575757576</v>
+        <v>0.8022424242424242</v>
       </c>
       <c r="B23" t="n">
-        <v>5936.732753326794</v>
+        <v>5023.632297620558</v>
       </c>
       <c r="C23" t="n">
-        <v>431.2372821999722</v>
+        <v>248.5728820954733</v>
       </c>
       <c r="D23" t="n">
-        <v>42.44384886313545</v>
+        <v>40.93185219389133</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7830820421603265</v>
+        <v>0.630382318097222</v>
       </c>
       <c r="F23" t="n">
-        <v>10.93215773484724</v>
+        <v>8.931722251155033</v>
       </c>
       <c r="G23" t="n">
-        <v>1.171255102867324</v>
+        <v>0.422566790558778</v>
       </c>
       <c r="H23" t="n">
-        <v>2.23395604756657e+21</v>
+        <v>4.023945909596082e+20</v>
       </c>
       <c r="I23" t="n">
-        <v>1.765667964006252e+21</v>
+        <v>2.54375826906085e+20</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.6321551845402885</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.4615555555555556</v>
+        <v>0.8404444444444444</v>
       </c>
       <c r="B24" t="n">
-        <v>5928.713430676257</v>
+        <v>5028.823929261816</v>
       </c>
       <c r="C24" t="n">
-        <v>430.2551618905309</v>
+        <v>246.3664784451158</v>
       </c>
       <c r="D24" t="n">
-        <v>42.44867793373786</v>
+        <v>40.90295067476975</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7834136504995379</v>
+        <v>0.6234975025537818</v>
       </c>
       <c r="F24" t="n">
-        <v>10.91041626914134</v>
+        <v>8.940561271027704</v>
       </c>
       <c r="G24" t="n">
-        <v>1.164373895145711</v>
+        <v>0.4200916236824631</v>
       </c>
       <c r="H24" t="n">
-        <v>2.240305754256194e+21</v>
+        <v>3.913181019771199e+20</v>
       </c>
       <c r="I24" t="n">
-        <v>1.771296275251311e+21</v>
+        <v>2.446777036330072e+20</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.6252654870724927</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.4825353535353535</v>
+        <v>0.8786464646464647</v>
       </c>
       <c r="B25" t="n">
-        <v>5920.285623564573</v>
+        <v>5027.83921316482</v>
       </c>
       <c r="C25" t="n">
-        <v>428.0800376313587</v>
+        <v>239.6497548980807</v>
       </c>
       <c r="D25" t="n">
-        <v>42.45362154627175</v>
+        <v>40.8891543831341</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7816739152715855</v>
+        <v>0.6067365957250386</v>
       </c>
       <c r="F25" t="n">
-        <v>10.88765194396727</v>
+        <v>8.938882661888188</v>
       </c>
       <c r="G25" t="n">
-        <v>1.154085999329971</v>
+        <v>0.4084031116217777</v>
       </c>
       <c r="H25" t="n">
-        <v>2.24671086852155e+21</v>
+        <v>3.858839698012545e+20</v>
       </c>
       <c r="I25" t="n">
-        <v>1.77226900606393e+21</v>
+        <v>2.347927892398637e+20</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.6084543738906575</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.5035151515151515</v>
+        <v>0.9168484848484848</v>
       </c>
       <c r="B26" t="n">
-        <v>5912.003624804486</v>
+        <v>5014.382295858458</v>
       </c>
       <c r="C26" t="n">
-        <v>425.6033677529034</v>
+        <v>238.8050682984971</v>
       </c>
       <c r="D26" t="n">
-        <v>42.45791939356296</v>
+        <v>40.90296543548376</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7793304322547477</v>
+        <v>0.6078474790898343</v>
       </c>
       <c r="F26" t="n">
-        <v>10.86536566796476</v>
+        <v>8.916040121421149</v>
       </c>
       <c r="G26" t="n">
-        <v>1.143115071458702</v>
+        <v>0.4037627741890493</v>
       </c>
       <c r="H26" t="n">
-        <v>2.251768997912987e+21</v>
+        <v>3.902505997470982e+20</v>
       </c>
       <c r="I26" t="n">
-        <v>1.770790459595955e+21</v>
+        <v>2.378702378465492e+20</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.609532023783438</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.5244949494949495</v>
+        <v>0.955050505050505</v>
       </c>
       <c r="B27" t="n">
-        <v>5903.925224852729</v>
+        <v>4992.000349684523</v>
       </c>
       <c r="C27" t="n">
-        <v>422.936867142097</v>
+        <v>240.3344719935753</v>
       </c>
       <c r="D27" t="n">
-        <v>42.46143227252033</v>
+        <v>40.93424253966755</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7765685713949889</v>
+        <v>0.6172382287995364</v>
       </c>
       <c r="F27" t="n">
-        <v>10.84370784685022</v>
+        <v>8.878445969648295</v>
       </c>
       <c r="G27" t="n">
-        <v>1.131799684930566</v>
+        <v>0.4010165351829899</v>
       </c>
       <c r="H27" t="n">
-        <v>2.255188876992636e+21</v>
+        <v>4.009516406810014e+20</v>
       </c>
       <c r="I27" t="n">
-        <v>1.767056190376915e+21</v>
+        <v>2.481444086675426e+20</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.6188886226929478</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.5454747474747474</v>
+        <v>0.9932525252525253</v>
       </c>
       <c r="B28" t="n">
-        <v>5896.098575130089</v>
+        <v>4967.002019321072</v>
       </c>
       <c r="C28" t="n">
-        <v>420.1755375981427</v>
+        <v>236.8852171466727</v>
       </c>
       <c r="D28" t="n">
-        <v>42.46403000270796</v>
+        <v>40.96713678924834</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7735479790534373</v>
+        <v>0.614518906653756</v>
       </c>
       <c r="F28" t="n">
-        <v>10.8228005628292</v>
+        <v>8.83704241266244</v>
       </c>
       <c r="G28" t="n">
-        <v>1.120416881753002</v>
+        <v>0.3894289884487012</v>
       </c>
       <c r="H28" t="n">
-        <v>2.256695422969313e+21</v>
+        <v>4.124276458971192e+20</v>
       </c>
       <c r="I28" t="n">
-        <v>1.761225566867821e+21</v>
+        <v>2.540954165876574e+20</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.6160969544971822</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.5664545454545454</v>
+        <v>1.031454545454545</v>
       </c>
       <c r="B29" t="n">
-        <v>5888.573089834988</v>
+        <v>4951.373665325483</v>
       </c>
       <c r="C29" t="n">
-        <v>417.417853342253</v>
+        <v>234.1798361146977</v>
       </c>
       <c r="D29" t="n">
-        <v>42.46557728361371</v>
+        <v>40.9764068848193</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7704364888399964</v>
+        <v>0.6113417498783726</v>
       </c>
       <c r="F29" t="n">
-        <v>10.80276794881121</v>
+        <v>8.811469878366848</v>
       </c>
       <c r="G29" t="n">
-        <v>1.109255096204137</v>
+        <v>0.3813971238102347</v>
       </c>
       <c r="H29" t="n">
-        <v>2.256006337418378e+21</v>
+        <v>4.150640717945209e+20</v>
       </c>
       <c r="I29" t="n">
-        <v>1.753478769585069e+21</v>
+        <v>2.543812039441939e+20</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.6128721352450044</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.5874343434343434</v>
+        <v>1.069656565656566</v>
       </c>
       <c r="B30" t="n">
-        <v>5881.39991688163</v>
+        <v>4947.424849899674</v>
       </c>
       <c r="C30" t="n">
-        <v>414.7663945045842</v>
+        <v>243.2325343435444</v>
       </c>
       <c r="D30" t="n">
-        <v>42.46593263208331</v>
+        <v>40.96092199407293</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7674111451893776</v>
+        <v>0.6359884310036945</v>
       </c>
       <c r="F30" t="n">
-        <v>10.7837369598319</v>
+        <v>8.805046259581934</v>
       </c>
       <c r="G30" t="n">
-        <v>1.098605809467424</v>
+        <v>0.3952026781265862</v>
       </c>
       <c r="H30" t="n">
-        <v>2.252832381022518e+21</v>
+        <v>4.083884215309109e+20</v>
       </c>
       <c r="I30" t="n">
-        <v>1.744016215117948e+21</v>
+        <v>2.603763090921881e+20</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.6375702526436104</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.6084141414141414</v>
+        <v>1.107858585858586</v>
       </c>
       <c r="B31" t="n">
-        <v>5874.632469842216</v>
+        <v>4948.694521627879</v>
       </c>
       <c r="C31" t="n">
-        <v>412.3286128362421</v>
+        <v>258.2481130051486</v>
       </c>
       <c r="D31" t="n">
-        <v>42.46494716528444</v>
+        <v>40.93441064001519</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7646594026160226</v>
+        <v>0.6749037289843771</v>
       </c>
       <c r="F31" t="n">
-        <v>10.76583946337139</v>
+        <v>8.807109985127036</v>
       </c>
       <c r="G31" t="n">
-        <v>1.088776499228255</v>
+        <v>0.4199200056791287</v>
       </c>
       <c r="H31" t="n">
-        <v>2.24687809674967e+21</v>
+        <v>3.977969636067985e+20</v>
       </c>
       <c r="I31" t="n">
-        <v>1.733058003312376e+21</v>
+        <v>2.691437911377368e+20</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.6765858358933361</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.6293939393939394</v>
+        <v>1.146060606060606</v>
       </c>
       <c r="B32" t="n">
-        <v>5868.237287301143</v>
+        <v>4945.761298639776</v>
       </c>
       <c r="C32" t="n">
-        <v>410.2052331317847</v>
+        <v>262.2360099602047</v>
       </c>
       <c r="D32" t="n">
-        <v>42.46265046295588</v>
+        <v>40.91587658618862</v>
       </c>
       <c r="E32" t="n">
-        <v>0.762380582090916</v>
+        <v>0.6861388141338857</v>
       </c>
       <c r="F32" t="n">
-        <v>10.748977313057</v>
+        <v>8.802344651981974</v>
       </c>
       <c r="G32" t="n">
-        <v>1.080001025928615</v>
+        <v>0.4256536314913597</v>
       </c>
       <c r="H32" t="n">
-        <v>2.23821247630089e+21</v>
+        <v>3.90280790302181e+20</v>
       </c>
       <c r="I32" t="n">
-        <v>1.721124753956329e+21</v>
+        <v>2.684510200305247e+20</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.6878407205813851</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.6503737373737374</v>
+        <v>1.184262626262626</v>
       </c>
       <c r="B33" t="n">
-        <v>5861.568179471628</v>
+        <v>4942.823858599285</v>
       </c>
       <c r="C33" t="n">
-        <v>408.4183355209385</v>
+        <v>255.1368361677668</v>
       </c>
       <c r="D33" t="n">
-        <v>42.46035196123988</v>
+        <v>40.89923652480632</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7607878220202685</v>
+        <v>0.6683575526149379</v>
       </c>
       <c r="F33" t="n">
-        <v>10.73144555065918</v>
+        <v>8.797580878868397</v>
       </c>
       <c r="G33" t="n">
-        <v>1.072010180411905</v>
+        <v>0.4133994531086373</v>
       </c>
       <c r="H33" t="n">
-        <v>2.229431667992308e+21</v>
+        <v>3.836324963819405e+20</v>
       </c>
       <c r="I33" t="n">
-        <v>1.710683146026658e+21</v>
+        <v>2.570366040782187e+20</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.6700073807676495</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.6713535353535354</v>
+        <v>1.222464646464646</v>
       </c>
       <c r="B34" t="n">
-        <v>5854.448435437444</v>
+        <v>4938.588146282838</v>
       </c>
       <c r="C34" t="n">
-        <v>407.0634450516507</v>
+        <v>247.3738445560989</v>
       </c>
       <c r="D34" t="n">
-        <v>42.45838659209359</v>
+        <v>40.88530014653617</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7601093877741218</v>
+        <v>0.6491336492329112</v>
       </c>
       <c r="F34" t="n">
-        <v>10.71278827818192</v>
+        <v>8.790726523502524</v>
       </c>
       <c r="G34" t="n">
-        <v>1.064963604035343</v>
+        <v>0.399800056602998</v>
       </c>
       <c r="H34" t="n">
-        <v>2.221185922138149e+21</v>
+        <v>3.780283729514715e+20</v>
       </c>
       <c r="I34" t="n">
-        <v>1.702722255614618e+21</v>
+        <v>2.459924771816956e+20</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.6507249052791979</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.6923333333333334</v>
+        <v>1.260666666666667</v>
       </c>
       <c r="B35" t="n">
-        <v>5846.88408333622</v>
+        <v>4927.464799639524</v>
       </c>
       <c r="C35" t="n">
-        <v>406.1750346464005</v>
+        <v>248.0040609499988</v>
       </c>
       <c r="D35" t="n">
-        <v>42.45675005318579</v>
+        <v>40.88412632024548</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7604142053990873</v>
+        <v>0.6537289143927928</v>
       </c>
       <c r="F35" t="n">
-        <v>10.69303267582836</v>
+        <v>8.772809404946893</v>
       </c>
       <c r="G35" t="n">
-        <v>1.058943360135769</v>
+        <v>0.398136441133757</v>
       </c>
       <c r="H35" t="n">
-        <v>2.213464415812678e+21</v>
+        <v>3.768153061370818e+20</v>
       </c>
       <c r="I35" t="n">
-        <v>1.697363451505426e+21</v>
+        <v>2.469279385541821e+20</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.6553023046902243</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.7133131313131313</v>
+        <v>1.298868686868687</v>
       </c>
       <c r="B36" t="n">
-        <v>5839.182818134995</v>
+        <v>4910.47524361619</v>
       </c>
       <c r="C36" t="n">
-        <v>405.3092870830217</v>
+        <v>255.2360678062591</v>
       </c>
       <c r="D36" t="n">
-        <v>42.45504636706889</v>
+        <v>40.89418512332848</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7607962662918791</v>
+        <v>0.6774557861211711</v>
       </c>
       <c r="F36" t="n">
-        <v>10.67299027539107</v>
+        <v>8.745674899789559</v>
       </c>
       <c r="G36" t="n">
-        <v>1.052936904453107</v>
+        <v>0.4055466518060759</v>
       </c>
       <c r="H36" t="n">
-        <v>2.205554850594021e+21</v>
+        <v>3.794474629169936e+20</v>
       </c>
       <c r="I36" t="n">
-        <v>1.692026646178183e+21</v>
+        <v>2.57660368545299e+20</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.6790409575136988</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.7342929292929293</v>
+        <v>1.337070707070707</v>
       </c>
       <c r="B37" t="n">
-        <v>5831.315211499426</v>
+        <v>4888.611943016758</v>
       </c>
       <c r="C37" t="n">
-        <v>404.2438914323631</v>
+        <v>263.3692761726319</v>
       </c>
       <c r="D37" t="n">
-        <v>42.45331447459918</v>
+        <v>40.9165212793052</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7608453544402783</v>
+        <v>0.7053098422354854</v>
       </c>
       <c r="F37" t="n">
-        <v>10.65258849224799</v>
+        <v>8.711166565768979</v>
       </c>
       <c r="G37" t="n">
-        <v>1.046354925901311</v>
+        <v>0.4129233277214532</v>
       </c>
       <c r="H37" t="n">
-        <v>2.197529674951275e+21</v>
+        <v>3.864871964472123e+20</v>
       </c>
       <c r="I37" t="n">
-        <v>1.685856034634698e+21</v>
+        <v>2.732081480583629e+20</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.7069009027202757</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.7552727272727273</v>
+        <v>1.375272727272727</v>
       </c>
       <c r="B38" t="n">
-        <v>5823.21605183965</v>
+        <v>4862.968164947622</v>
       </c>
       <c r="C38" t="n">
-        <v>402.8826237019493</v>
+        <v>263.5707319744735</v>
       </c>
       <c r="D38" t="n">
-        <v>42.45164043685785</v>
+        <v>40.94994704778607</v>
       </c>
       <c r="E38" t="n">
-        <v>0.76039401972414</v>
+        <v>0.7133132522512059</v>
       </c>
       <c r="F38" t="n">
-        <v>10.63166368281809</v>
+        <v>8.671275845684573</v>
       </c>
       <c r="G38" t="n">
-        <v>1.038924775757648</v>
+        <v>0.4067727067034964</v>
       </c>
       <c r="H38" t="n">
-        <v>2.189544631825892e+21</v>
+        <v>3.977941774389053e+20</v>
       </c>
       <c r="I38" t="n">
-        <v>1.678608702003438e+21</v>
+        <v>2.843647969748704e+20</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.7148540956674616</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.7762525252525253</v>
+        <v>1.413474747474748</v>
       </c>
       <c r="B39" t="n">
-        <v>5814.915143766757</v>
+        <v>4834.759196596306</v>
       </c>
       <c r="C39" t="n">
-        <v>401.3082047760989</v>
+        <v>253.4842532410848</v>
       </c>
       <c r="D39" t="n">
-        <v>42.44998678934458</v>
+        <v>40.98756116370907</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7595865024987088</v>
+        <v>0.6940443964278867</v>
       </c>
       <c r="F39" t="n">
-        <v>10.6102990528876</v>
+        <v>8.628118813207013</v>
       </c>
       <c r="G39" t="n">
-        <v>1.030881959854856</v>
+        <v>0.3844178537207941</v>
       </c>
       <c r="H39" t="n">
-        <v>2.181534206723933e+21</v>
+        <v>4.109861058000904e+20</v>
       </c>
       <c r="I39" t="n">
-        <v>1.670564500457114e+21</v>
+        <v>2.85829738804834e+20</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.6954729971914568</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.7972323232323233</v>
+        <v>1.451676767676768</v>
       </c>
       <c r="B40" t="n">
-        <v>5806.444468914768</v>
+        <v>4813.912682602444</v>
       </c>
       <c r="C40" t="n">
-        <v>399.6087932587516</v>
+        <v>245.6953997131425</v>
       </c>
       <c r="D40" t="n">
-        <v>42.44831279281472</v>
+        <v>41.00549541095423</v>
       </c>
       <c r="E40" t="n">
-        <v>0.758578352722604</v>
+        <v>0.6785573685008003</v>
       </c>
       <c r="F40" t="n">
-        <v>10.58858249483566</v>
+        <v>8.596709305601875</v>
       </c>
       <c r="G40" t="n">
-        <v>1.022475478918441</v>
+        <v>0.3677781076914961</v>
       </c>
       <c r="H40" t="n">
-        <v>2.173427808724873e+21</v>
+        <v>4.169001094397844e+20</v>
       </c>
       <c r="I40" t="n">
-        <v>1.6620197138401e+21</v>
+        <v>2.834523248261825e+20</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.6799046543956915</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.8182121212121213</v>
+        <v>1.489878787878788</v>
       </c>
       <c r="B41" t="n">
-        <v>5797.838461143314</v>
+        <v>4808.229123438</v>
       </c>
       <c r="C41" t="n">
-        <v>397.8785953554484</v>
+        <v>250.1477634137949</v>
       </c>
       <c r="D41" t="n">
-        <v>42.44657400419414</v>
+        <v>40.98798029279103</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7575378153873329</v>
+        <v>0.6924880412142923</v>
       </c>
       <c r="F41" t="n">
-        <v>10.566606444147</v>
+        <v>8.588216880032178</v>
       </c>
       <c r="G41" t="n">
-        <v>1.013968518420821</v>
+        <v>0.3731077795373638</v>
       </c>
       <c r="H41" t="n">
-        <v>2.165148961355415e+21</v>
+        <v>4.092569390455184e+20</v>
       </c>
       <c r="I41" t="n">
-        <v>1.653289101156052e+21</v>
+        <v>2.839627085831216e+20</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.6938494659257045</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.8391919191919193</v>
+        <v>1.528080808080808</v>
       </c>
       <c r="B42" t="n">
-        <v>5789.13427936787</v>
+        <v>4813.189174528425</v>
       </c>
       <c r="C42" t="n">
-        <v>396.2184937246928</v>
+        <v>255.6204413675335</v>
       </c>
       <c r="D42" t="n">
-        <v>42.44472184565777</v>
+        <v>40.94642388646962</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7566472521262007</v>
+        <v>0.7061804345665053</v>
       </c>
       <c r="F42" t="n">
-        <v>10.54446945951813</v>
+        <v>8.595626576492613</v>
       </c>
       <c r="G42" t="n">
-        <v>1.005634152316716</v>
+        <v>0.3824609209322752</v>
       </c>
       <c r="H42" t="n">
-        <v>2.156614891639442e+21</v>
+        <v>3.929369506382011e+20</v>
       </c>
       <c r="I42" t="n">
-        <v>1.644707883145052e+21</v>
+        <v>2.780346439094685e+20</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.7075808051594275</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.8601717171717171</v>
+        <v>1.566282828282828</v>
       </c>
       <c r="B43" t="n">
-        <v>5780.372072949332</v>
+        <v>4812.863679615</v>
       </c>
       <c r="C43" t="n">
-        <v>394.7366909270571</v>
+        <v>252.7838247109269</v>
       </c>
       <c r="D43" t="n">
-        <v>42.44270317966924</v>
+        <v>40.91417567046366</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7561045835358349</v>
+        <v>0.6984384210968899</v>
       </c>
       <c r="F43" t="n">
-        <v>10.52227592716351</v>
+        <v>8.595139601957651</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9977671574004109</v>
+        <v>0.3781394313233413</v>
       </c>
       <c r="H43" t="n">
-        <v>2.147735803930797e+21</v>
+        <v>3.804460182550734e+20</v>
       </c>
       <c r="I43" t="n">
-        <v>1.63663356649768e+21</v>
+        <v>2.662447429593414e+20</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.6998226559985581</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.8811515151515151</v>
+        <v>1.604484848484848</v>
       </c>
       <c r="B44" t="n">
-        <v>5771.595232885838</v>
+        <v>4802.202928090892</v>
       </c>
       <c r="C44" t="n">
-        <v>393.5493611149967</v>
+        <v>255.124944807372</v>
       </c>
       <c r="D44" t="n">
-        <v>42.44045990061392</v>
+        <v>40.90405175954323</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7561247302520123</v>
+        <v>0.7080401253180109</v>
       </c>
       <c r="F44" t="n">
-        <v>10.50013659641092</v>
+        <v>8.579245528467194</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9906701383777949</v>
+        <v>0.3790904213697296</v>
       </c>
       <c r="H44" t="n">
-        <v>2.138414428560545e+21</v>
+        <v>3.759174159073618e+20</v>
       </c>
       <c r="I44" t="n">
-        <v>1.629446833886596e+21</v>
+        <v>2.666824234721797e+20</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.709417579998206</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.9021313131313131</v>
+        <v>1.642686868686869</v>
       </c>
       <c r="B45" t="n">
-        <v>5762.850620101584</v>
+        <v>4785.07663803743</v>
       </c>
       <c r="C45" t="n">
-        <v>392.7813012795793</v>
+        <v>263.7162054451209</v>
       </c>
       <c r="D45" t="n">
-        <v>42.43792855695828</v>
+        <v>40.90779930235643</v>
       </c>
       <c r="E45" t="n">
-        <v>0.7569410232650402</v>
+        <v>0.7371315254387111</v>
       </c>
       <c r="F45" t="n">
-        <v>10.47816923779082</v>
+        <v>8.553934618753157</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9846727655535434</v>
+        <v>0.3876373540470767</v>
       </c>
       <c r="H45" t="n">
-        <v>2.128545741024548e+21</v>
+        <v>3.762156115710588e+20</v>
       </c>
       <c r="I45" t="n">
-        <v>1.623552748851356e+21</v>
+        <v>2.778439536696265e+20</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.7385231902242525</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.9231111111111111</v>
+        <v>1.680888888888889</v>
       </c>
       <c r="B46" t="n">
-        <v>5754.187831951203</v>
+        <v>4765.677519874333</v>
       </c>
       <c r="C46" t="n">
-        <v>392.5680525264239</v>
+        <v>273.5436587386782</v>
       </c>
       <c r="D46" t="n">
-        <v>42.43504126274884</v>
+        <v>40.91642833539662</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7588096544075755</v>
+        <v>0.7708383469259955</v>
       </c>
       <c r="F46" t="n">
-        <v>10.45649665765207</v>
+        <v>8.525594838441888</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9801194127018964</v>
+        <v>0.3971527647928092</v>
       </c>
       <c r="H46" t="n">
-        <v>2.11801897068632e+21</v>
+        <v>3.782188049375487e+20</v>
       </c>
       <c r="I46" t="n">
-        <v>1.619388575238321e+21</v>
+        <v>2.92077445692192e+20</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.7722446421996909</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.9440909090909091</v>
+        <v>1.719090909090909</v>
       </c>
       <c r="B47" t="n">
-        <v>5745.654437732074</v>
+        <v>4746.914208319427</v>
       </c>
       <c r="C47" t="n">
-        <v>393.0643532283962</v>
+        <v>278.9633691805807</v>
       </c>
       <c r="D47" t="n">
-        <v>42.43173204534736</v>
+        <v>40.92473623034584</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7620274527909917</v>
+        <v>0.792337803309532</v>
       </c>
       <c r="F47" t="n">
-        <v>10.43523444015454</v>
+        <v>8.498515441488639</v>
       </c>
       <c r="G47" t="n">
-        <v>0.97740256112232</v>
+        <v>0.4001863393873589</v>
       </c>
       <c r="H47" t="n">
-        <v>2.106729023142132e+21</v>
+        <v>3.801627573870973e+20</v>
       </c>
       <c r="I47" t="n">
-        <v>1.617466813348005e+21</v>
+        <v>3.017488012503611e+20</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.7937358286338083</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.9650707070707071</v>
+        <v>1.757292929292929</v>
       </c>
       <c r="B48" t="n">
-        <v>5737.162035476138</v>
+        <v>4726.71860954308</v>
       </c>
       <c r="C48" t="n">
-        <v>394.0819221902975</v>
+        <v>281.0810617004469</v>
       </c>
       <c r="D48" t="n">
-        <v>42.42808774305605</v>
+        <v>40.93803403703453</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7662636852668115</v>
+        <v>0.805189403482533</v>
       </c>
       <c r="F48" t="n">
-        <v>10.4141594551151</v>
+        <v>8.46973139782831</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9759932949003458</v>
+        <v>0.398011454318636</v>
       </c>
       <c r="H48" t="n">
-        <v>2.094826168771593e+21</v>
+        <v>3.839470215302572e+20</v>
       </c>
       <c r="I48" t="n">
-        <v>1.617150286637939e+21</v>
+        <v>3.096761217302706e+20</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.8065595104658635</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.9860505050505051</v>
+        <v>1.795494949494949</v>
       </c>
       <c r="B49" t="n">
-        <v>5728.520431750037</v>
+        <v>4701.210888678127</v>
       </c>
       <c r="C49" t="n">
-        <v>395.2344162494065</v>
+        <v>276.1331450474137</v>
       </c>
       <c r="D49" t="n">
-        <v>42.42433258399214</v>
+        <v>40.96667773161255</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7708249886415384</v>
+        <v>0.7996225545992047</v>
       </c>
       <c r="F49" t="n">
-        <v>10.39280141888988</v>
+        <v>8.433909437772186</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9748324502140208</v>
+        <v>0.3845821161378915</v>
       </c>
       <c r="H49" t="n">
-        <v>2.082694411420967e+21</v>
+        <v>3.934326490144982e+20</v>
       </c>
       <c r="I49" t="n">
-        <v>1.617235183880852e+21</v>
+        <v>3.151087400351155e+20</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8009216846248659</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1.007030303030303</v>
+        <v>1.83369696969697</v>
       </c>
       <c r="B50" t="n">
-        <v>5719.691883220881</v>
+        <v>4673.039966034011</v>
       </c>
       <c r="C50" t="n">
-        <v>396.5108833113108</v>
+        <v>259.3962873523513</v>
       </c>
       <c r="D50" t="n">
-        <v>42.42053026997947</v>
+        <v>41.00216584635173</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7757035995282625</v>
+        <v>0.7602400208484508</v>
       </c>
       <c r="F50" t="n">
-        <v>10.37107181908333</v>
+        <v>8.395033953665465</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9738741486896754</v>
+        <v>0.354663202684535</v>
       </c>
       <c r="H50" t="n">
-        <v>2.070452351838956e+21</v>
+        <v>4.05766522589515e+20</v>
       </c>
       <c r="I50" t="n">
-        <v>1.617782411492344e+21</v>
+        <v>3.089558849220546e+20</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.761412949866747</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1.028010101010101</v>
+        <v>1.87189898989899</v>
       </c>
       <c r="B51" t="n">
-        <v>5710.637150894339</v>
+        <v>4652.685468605419</v>
       </c>
       <c r="C51" t="n">
-        <v>397.9013275045389</v>
+        <v>241.0523397450753</v>
       </c>
       <c r="D51" t="n">
-        <v>42.41674817627388</v>
+        <v>41.01869959625702</v>
       </c>
       <c r="E51" t="n">
-        <v>0.7808942380712474</v>
+        <v>0.7126723763902464</v>
       </c>
       <c r="F51" t="n">
-        <v>10.34888046056796</v>
+        <v>8.367390195248111</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9730678820517576</v>
+        <v>0.3251782791788355</v>
       </c>
       <c r="H51" t="n">
-        <v>2.058222998376185e+21</v>
+        <v>4.111727213443616e+20</v>
       </c>
       <c r="I51" t="n">
-        <v>1.618863728721204e+21</v>
+        <v>2.934667967847297e+20</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.7137311926365565</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.048989898989899</v>
+        <v>1.91010101010101</v>
       </c>
       <c r="B52" t="n">
-        <v>5701.314606011353</v>
+        <v>4645.552745684165</v>
       </c>
       <c r="C52" t="n">
-        <v>399.3949943167649</v>
+        <v>238.9979122795104</v>
       </c>
       <c r="D52" t="n">
-        <v>42.41305857655149</v>
+        <v>41.00028242617568</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7863910592622296</v>
+        <v>0.708769922319148</v>
       </c>
       <c r="F52" t="n">
-        <v>10.32613295900856</v>
+        <v>8.357790948431425</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9723682869080063</v>
+        <v>0.3208834013376564</v>
       </c>
       <c r="H52" t="n">
-        <v>2.046135527115557e+21</v>
+        <v>4.032062924968121e+20</v>
       </c>
       <c r="I52" t="n">
-        <v>1.620557539190411e+21</v>
+        <v>2.861994648895347e+20</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.7098090238554436</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1.069969696969697</v>
+        <v>1.94830303030303</v>
       </c>
       <c r="B53" t="n">
-        <v>5691.680020489879</v>
+        <v>4641.649432594172</v>
       </c>
       <c r="C53" t="n">
-        <v>400.9802835590224</v>
+        <v>253.5458113319313</v>
       </c>
       <c r="D53" t="n">
-        <v>42.40953913449315</v>
+        <v>40.96840991526339</v>
       </c>
       <c r="E53" t="n">
-        <v>0.7921875785462027</v>
+        <v>0.7531781802695717</v>
       </c>
       <c r="F53" t="n">
-        <v>10.30273073165005</v>
+        <v>8.352557071841328</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9717204716938801</v>
+        <v>0.3395326961025749</v>
       </c>
       <c r="H53" t="n">
-        <v>2.03432604144537e+21</v>
+        <v>3.903131589901863e+20</v>
       </c>
       <c r="I53" t="n">
-        <v>1.622949586158581e+21</v>
+        <v>2.944032070995445e+20</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.7542743571885228</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1.090949494949495</v>
+        <v>1.986505050505051</v>
       </c>
       <c r="B54" t="n">
-        <v>5681.6863450703</v>
+        <v>4629.414534533363</v>
       </c>
       <c r="C54" t="n">
-        <v>402.6446550841614</v>
+        <v>269.5168259090804</v>
       </c>
       <c r="D54" t="n">
-        <v>42.40627343939636</v>
+        <v>40.95162808722446</v>
       </c>
       <c r="E54" t="n">
-        <v>0.7982765860282725</v>
+        <v>0.8048588144686384</v>
       </c>
       <c r="F54" t="n">
-        <v>10.27857059800048</v>
+        <v>8.336239510998563</v>
       </c>
       <c r="G54" t="n">
-        <v>0.971068016506652</v>
+        <v>0.3579858086239107</v>
       </c>
       <c r="H54" t="n">
-        <v>2.022938402591681e+21</v>
+        <v>3.830678200059741e+20</v>
       </c>
       <c r="I54" t="n">
-        <v>1.626134268567114e+21</v>
+        <v>3.087540507202982e+20</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.8060036228453831</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1.111929292929293</v>
+        <v>2.024707070707071</v>
       </c>
       <c r="B55" t="n">
-        <v>5671.283474485302</v>
+        <v>4611.467716184831</v>
       </c>
       <c r="C55" t="n">
-        <v>404.3745265485809</v>
+        <v>281.7666661675224</v>
       </c>
       <c r="D55" t="n">
-        <v>42.40335159065177</v>
+        <v>40.95032443819757</v>
       </c>
       <c r="E55" t="n">
-        <v>0.804650047211281</v>
+        <v>0.8480026926094789</v>
       </c>
       <c r="F55" t="n">
-        <v>10.25354462758253</v>
+        <v>8.312544399172946</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9703522427825907</v>
+        <v>0.3697785207429892</v>
       </c>
       <c r="H55" t="n">
-        <v>2.01212528681603e+21</v>
+        <v>3.814813374706147e+20</v>
       </c>
       <c r="I55" t="n">
-        <v>1.630215948066377e+21</v>
+        <v>3.239419995413527e+20</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.8491686688770345</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.132909090909091</v>
+        <v>2.062909090909091</v>
       </c>
       <c r="B56" t="n">
-        <v>5660.417998965057</v>
+        <v>4591.547710309756</v>
       </c>
       <c r="C56" t="n">
-        <v>406.155162432959</v>
+        <v>281.9912129051404</v>
       </c>
       <c r="D56" t="n">
-        <v>42.40087083656191</v>
+        <v>40.96095421867219</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8112989877573382</v>
+        <v>0.8560582868443521</v>
       </c>
       <c r="F56" t="n">
-        <v>10.22753991786946</v>
+        <v>8.286577061450286</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9695073877941082</v>
+        <v>0.3651288819167636</v>
       </c>
       <c r="H56" t="n">
-        <v>2.002049441570728e+21</v>
+        <v>3.843535945899224e+20</v>
       </c>
       <c r="I56" t="n">
-        <v>1.635310348218386e+21</v>
+        <v>3.294646440323189e+20</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.8571915253812935</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1.153888888888889</v>
+        <v>2.101111111111111</v>
       </c>
       <c r="B57" t="n">
-        <v>5649.054503830881</v>
+        <v>4569.891637390022</v>
       </c>
       <c r="C57" t="n">
-        <v>407.9362937090632</v>
+        <v>270.0192984057053</v>
       </c>
       <c r="D57" t="n">
-        <v>42.39890635144663</v>
+        <v>40.97943391841658</v>
       </c>
       <c r="E57" t="n">
-        <v>0.8181384032206095</v>
+        <v>0.8275018307798965</v>
       </c>
       <c r="F57" t="n">
-        <v>10.20048942444108</v>
+        <v>8.258741463289567</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9683970924704691</v>
+        <v>0.3445148190005329</v>
       </c>
       <c r="H57" t="n">
-        <v>1.992835541339045e+21</v>
+        <v>3.902071977823889e+20</v>
       </c>
       <c r="I57" t="n">
-        <v>1.641355480733492e+21</v>
+        <v>3.233071940388619e+20</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.8285526148063628</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1.174868686868687</v>
+        <v>2.139313131313131</v>
       </c>
       <c r="B58" t="n">
-        <v>5637.418357333527</v>
+        <v>4543.587271631683</v>
       </c>
       <c r="C58" t="n">
-        <v>409.2460907400736</v>
+        <v>250.4370174466125</v>
       </c>
       <c r="D58" t="n">
-        <v>42.39717265886622</v>
+        <v>41.00740062814529</v>
       </c>
       <c r="E58" t="n">
-        <v>0.8241570381922723</v>
+        <v>0.7764021643909436</v>
       </c>
       <c r="F58" t="n">
-        <v>10.17294473758723</v>
+        <v>8.225480598592684</v>
       </c>
       <c r="G58" t="n">
-        <v>0.966011528224006</v>
+        <v>0.3138156416370853</v>
       </c>
       <c r="H58" t="n">
-        <v>1.984011578350421e+21</v>
+        <v>3.996579674008806e+20</v>
       </c>
       <c r="I58" t="n">
-        <v>1.645954963131053e+21</v>
+        <v>3.106697114069223e+20</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.7773389666852361</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1.195848484848485</v>
+        <v>2.177515151515152</v>
       </c>
       <c r="B59" t="n">
-        <v>5625.534105831736</v>
+        <v>4518.334598813266</v>
       </c>
       <c r="C59" t="n">
-        <v>409.9459791083885</v>
+        <v>241.5525008909026</v>
       </c>
       <c r="D59" t="n">
-        <v>42.39566202506546</v>
+        <v>41.02766751459232</v>
       </c>
       <c r="E59" t="n">
-        <v>0.8290582969878664</v>
+        <v>0.7572525135232697</v>
       </c>
       <c r="F59" t="n">
-        <v>10.14497372286063</v>
+        <v>8.194111798430944</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9620547555234332</v>
+        <v>0.2974362961155081</v>
       </c>
       <c r="H59" t="n">
-        <v>1.975569822558582e+21</v>
+        <v>4.062850808804484e+20</v>
       </c>
       <c r="I59" t="n">
-        <v>1.648542311139578e+21</v>
+        <v>3.080136591831234e+20</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.7581220026973082</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1.216828282828283</v>
+        <v>2.215717171717172</v>
       </c>
       <c r="B60" t="n">
-        <v>5613.337985053059</v>
+        <v>4501.818103397065</v>
       </c>
       <c r="C60" t="n">
-        <v>410.0578502501226</v>
+        <v>253.2283443374698</v>
       </c>
       <c r="D60" t="n">
-        <v>42.39449217059983</v>
+        <v>41.02277523069476</v>
       </c>
       <c r="E60" t="n">
-        <v>0.8328920347988124</v>
+        <v>0.7996913378968652</v>
       </c>
       <c r="F60" t="n">
-        <v>10.11643751560939</v>
+        <v>8.173890742381644</v>
       </c>
       <c r="G60" t="n">
-        <v>0.956573518815757</v>
+        <v>0.3082412183634564</v>
       </c>
       <c r="H60" t="n">
-        <v>1.967709576144235e+21</v>
+        <v>4.033045543622719e+20</v>
       </c>
       <c r="I60" t="n">
-        <v>1.649417275894404e+21</v>
+        <v>3.228775547550953e+20</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.8005799866694976</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1.237808080808081</v>
+        <v>2.253919191919192</v>
       </c>
       <c r="B61" t="n">
-        <v>5600.752301401228</v>
+        <v>4490.235077306816</v>
       </c>
       <c r="C61" t="n">
-        <v>409.5902903510652</v>
+        <v>275.1674588176253</v>
       </c>
       <c r="D61" t="n">
-        <v>42.3938041384685</v>
+        <v>41.00352949272084</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8356855326287622</v>
+        <v>0.8734637374828272</v>
       </c>
       <c r="F61" t="n">
-        <v>10.08716865483216</v>
+        <v>8.159848425232644</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9495788201383462</v>
+        <v>0.3322371796212124</v>
       </c>
       <c r="H61" t="n">
-        <v>1.960667135784816e+21</v>
+        <v>3.949372262852899e+20</v>
       </c>
       <c r="I61" t="n">
-        <v>1.648864106054304e+21</v>
+        <v>3.453379301942586e+20</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.874412203282143</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.258787878787879</v>
+        <v>2.292121212121212</v>
       </c>
       <c r="B62" t="n">
-        <v>5587.693812885664</v>
+        <v>4476.624159105984</v>
       </c>
       <c r="C62" t="n">
-        <v>408.5537229470084</v>
+        <v>289.6552175007061</v>
       </c>
       <c r="D62" t="n">
-        <v>42.39375032005747</v>
+        <v>40.98756074071245</v>
       </c>
       <c r="E62" t="n">
-        <v>0.8374713041395283</v>
+        <v>0.9250517954417066</v>
       </c>
       <c r="F62" t="n">
-        <v>10.05699180371452</v>
+        <v>8.1434930912308</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9410814171274137</v>
+        <v>0.3463926215002517</v>
       </c>
       <c r="H62" t="n">
-        <v>1.954696387458367e+21</v>
+        <v>3.879016005598643e+20</v>
       </c>
       <c r="I62" t="n">
-        <v>1.647189181346158e+21</v>
+        <v>3.592082228220388e+20</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.9260292360319941</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1.279767676767677</v>
+        <v>2.330323232323232</v>
       </c>
       <c r="B63" t="n">
-        <v>5574.130843540614</v>
+        <v>4459.681974263799</v>
       </c>
       <c r="C63" t="n">
-        <v>406.9693330335306</v>
+        <v>296.174284600212</v>
       </c>
       <c r="D63" t="n">
-        <v>42.39436263292714</v>
+        <v>40.98071887738367</v>
       </c>
       <c r="E63" t="n">
-        <v>0.838288155081259</v>
+        <v>0.9530716069343191</v>
       </c>
       <c r="F63" t="n">
-        <v>10.02585499497521</v>
+        <v>8.123353237995683</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9311454927921343</v>
+        <v>0.349963585283807</v>
       </c>
       <c r="H63" t="n">
-        <v>1.949838122588723e+21</v>
+        <v>3.843039023465259e+20</v>
       </c>
       <c r="I63" t="n">
-        <v>1.644527143950587e+21</v>
+        <v>3.66643138645327e+20</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.9540447973768579</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1.300747474747475</v>
+        <v>2.368525252525253</v>
       </c>
       <c r="B64" t="n">
-        <v>5560.038940447465</v>
+        <v>4442.686399559598</v>
       </c>
       <c r="C64" t="n">
-        <v>404.8628525891687</v>
+        <v>297.7924065872622</v>
       </c>
       <c r="D64" t="n">
-        <v>42.39565236700517</v>
+        <v>40.9756322526406</v>
       </c>
       <c r="E64" t="n">
-        <v>0.8381818014432747</v>
+        <v>0.9656244766949352</v>
       </c>
       <c r="F64" t="n">
-        <v>9.993725540828853</v>
+        <v>8.103392050844349</v>
       </c>
       <c r="G64" t="n">
-        <v>0.919845833631566</v>
+        <v>0.3476388780251148</v>
       </c>
       <c r="H64" t="n">
-        <v>1.946097885677075e+21</v>
+        <v>3.814145127335271e+20</v>
       </c>
       <c r="I64" t="n">
-        <v>1.640989299951826e+21</v>
+        <v>3.686664912580244e+20</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.9665769889453342</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1.321727272727273</v>
+        <v>2.406727272727273</v>
       </c>
       <c r="B65" t="n">
-        <v>5545.367808622229</v>
+        <v>4428.596235394104</v>
       </c>
       <c r="C65" t="n">
-        <v>402.2600209715894</v>
+        <v>294.8377690662339</v>
       </c>
       <c r="D65" t="n">
-        <v>42.39768646596502</v>
+        <v>40.96498010692721</v>
       </c>
       <c r="E65" t="n">
-        <v>0.8372055928141721</v>
+        <v>0.9621369779307344</v>
       </c>
       <c r="F65" t="n">
-        <v>9.960514845485122</v>
+        <v>8.087026111715542</v>
       </c>
       <c r="G65" t="n">
-        <v>0.907250536633086</v>
+        <v>0.3407307052666674</v>
       </c>
       <c r="H65" t="n">
-        <v>1.943580117652007e+21</v>
+        <v>3.766110341474437e+20</v>
       </c>
       <c r="I65" t="n">
-        <v>1.636777924558957e+21</v>
+        <v>3.626986687854493e+20</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.963059060673863</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1.342707070707071</v>
+        <v>2.444929292929293</v>
       </c>
       <c r="B66" t="n">
-        <v>5530.061508534182</v>
+        <v>4414.391113033237</v>
       </c>
       <c r="C66" t="n">
-        <v>399.1898850688965</v>
+        <v>286.8383146009617</v>
       </c>
       <c r="D66" t="n">
-        <v>42.400541052215</v>
+        <v>40.95640531972466</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8354213456972368</v>
+        <v>0.9420663846165961</v>
       </c>
       <c r="F66" t="n">
-        <v>9.926125439250656</v>
+        <v>8.070693550923311</v>
       </c>
       <c r="G66" t="n">
-        <v>0.8934309891826409</v>
+        <v>0.3281103493639012</v>
       </c>
       <c r="H66" t="n">
-        <v>1.942406625862665e+21</v>
+        <v>3.726413710723978e+20</v>
       </c>
       <c r="I66" t="n">
-        <v>1.632118965891523e+21</v>
+        <v>3.51379644199722e+20</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.9429431927767754</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1.363686868686869</v>
+        <v>2.483131313131313</v>
       </c>
       <c r="B67" t="n">
-        <v>5514.057753297035</v>
+        <v>4395.27856268941</v>
       </c>
       <c r="C67" t="n">
-        <v>395.6851175800762</v>
+        <v>277.8771886816368</v>
       </c>
       <c r="D67" t="n">
-        <v>42.40430281303313</v>
+        <v>40.96220759228243</v>
       </c>
       <c r="E67" t="n">
-        <v>0.8329003755131502</v>
+        <v>0.9205895688284443</v>
       </c>
       <c r="F67" t="n">
-        <v>9.890451375433422</v>
+        <v>8.048981568246528</v>
       </c>
       <c r="G67" t="n">
-        <v>0.8784652097330433</v>
+        <v>0.3134853610728326</v>
       </c>
       <c r="H67" t="n">
-        <v>1.94272002050129e+21</v>
+        <v>3.738014999564785e+20</v>
       </c>
       <c r="I67" t="n">
-        <v>1.627266570163303e+21</v>
+        <v>3.444255863669557e+20</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.9214130665796069</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1.384666666666667</v>
+        <v>2.521333333333333</v>
       </c>
       <c r="B68" t="n">
-        <v>5497.303336954123</v>
+        <v>4366.452812456318</v>
       </c>
       <c r="C68" t="n">
-        <v>391.756537483491</v>
+        <v>271.7721204696063</v>
       </c>
       <c r="D68" t="n">
-        <v>42.40904684011183</v>
+        <v>40.9949360564612</v>
       </c>
       <c r="E68" t="n">
-        <v>0.8296650815694432</v>
+        <v>0.9122908594038813</v>
       </c>
       <c r="F68" t="n">
-        <v>9.853412171291371</v>
+        <v>8.016801893751747</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8623878798231691</v>
+        <v>0.3001999418574873</v>
       </c>
       <c r="H68" t="n">
-        <v>1.944648254976616e+21</v>
+        <v>3.846936786529774e+20</v>
       </c>
       <c r="I68" t="n">
-        <v>1.622359102353948e+21</v>
+        <v>3.512480473491691e+20</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.9130590566995546</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1.405646464646465</v>
+        <v>2.559535353535354</v>
       </c>
       <c r="B69" t="n">
-        <v>5480.096359308281</v>
+        <v>4330.566880115473</v>
       </c>
       <c r="C69" t="n">
-        <v>386.8470909423675</v>
+        <v>266.7863025977051</v>
       </c>
       <c r="D69" t="n">
-        <v>42.41433174838888</v>
+        <v>41.04570736718167</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8244207391055763</v>
+        <v>0.9104581563165015</v>
       </c>
       <c r="F69" t="n">
-        <v>9.815699141417269</v>
+        <v>7.977683143347721</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8441488601404169</v>
+        <v>0.2869641877992484</v>
       </c>
       <c r="H69" t="n">
-        <v>1.947470345756139e+21</v>
+        <v>4.027544813467213e+20</v>
       </c>
       <c r="I69" t="n">
-        <v>1.614246801540317e+21</v>
+        <v>3.669771794778094e+20</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.9111684573954819</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1.426626262626263</v>
+        <v>2.597737373737374</v>
       </c>
       <c r="B70" t="n">
-        <v>5462.53198585857</v>
+        <v>4295.032263367066</v>
       </c>
       <c r="C70" t="n">
-        <v>380.7130846233845</v>
+        <v>264.0974884422128</v>
       </c>
       <c r="D70" t="n">
-        <v>42.42000549608444</v>
+        <v>41.09291759036035</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8165744370468085</v>
+        <v>0.9162571423057939</v>
       </c>
       <c r="F70" t="n">
-        <v>9.777543223742351</v>
+        <v>7.939965002007042</v>
       </c>
       <c r="G70" t="n">
-        <v>0.823327072739933</v>
+        <v>0.27659458696269</v>
       </c>
       <c r="H70" t="n">
-        <v>1.950937859931775e+21</v>
+        <v>4.202283286038486e+20</v>
       </c>
       <c r="I70" t="n">
-        <v>1.601533966634482e+21</v>
+        <v>3.853153909248211e+20</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.9169191239557291</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1.447606060606061</v>
+        <v>2.635939393939394</v>
       </c>
       <c r="B71" t="n">
-        <v>5445.265693372108</v>
+        <v>4270.747797205569</v>
       </c>
       <c r="C71" t="n">
-        <v>374.690663696711</v>
+        <v>271.6021092259883</v>
       </c>
       <c r="D71" t="n">
-        <v>42.42507373056798</v>
+        <v>41.10641967681364</v>
       </c>
       <c r="E71" t="n">
-        <v>0.8087619002724724</v>
+        <v>0.9530402662918011</v>
       </c>
       <c r="F71" t="n">
-        <v>9.740368491992736</v>
+        <v>7.914764167301555</v>
       </c>
       <c r="G71" t="n">
-        <v>0.8031358951403983</v>
+        <v>0.279256881421179</v>
       </c>
       <c r="H71" t="n">
-        <v>1.953395512335908e+21</v>
+        <v>4.245888629123723e+20</v>
       </c>
       <c r="I71" t="n">
-        <v>1.588021088752726e+21</v>
+        <v>4.049274939545144e+20</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.9536931590174194</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1.468585858585859</v>
+        <v>2.674141414141414</v>
       </c>
       <c r="B72" t="n">
-        <v>5428.853458125338</v>
+        <v>4258.421979926673</v>
       </c>
       <c r="C72" t="n">
-        <v>369.9423232635739</v>
+        <v>290.9954024657401</v>
       </c>
       <c r="D72" t="n">
-        <v>42.42866515263942</v>
+        <v>41.08550721197712</v>
       </c>
       <c r="E72" t="n">
-        <v>0.8033480519567651</v>
+        <v>1.027010067373567</v>
       </c>
       <c r="F72" t="n">
-        <v>9.705338148084934</v>
+        <v>7.90215047633133</v>
       </c>
       <c r="G72" t="n">
-        <v>0.7862573449180287</v>
+        <v>0.2963898331391531</v>
       </c>
       <c r="H72" t="n">
-        <v>1.953373108893762e+21</v>
+        <v>4.151392025799633e+20</v>
       </c>
       <c r="I72" t="n">
-        <v>1.577197501799005e+21</v>
+        <v>4.266363772221755e+20</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1.027694745691953</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1.489565656565657</v>
+        <v>2.712343434343434</v>
       </c>
       <c r="B73" t="n">
-        <v>5413.190556934747</v>
+        <v>4246.864694208935</v>
       </c>
       <c r="C73" t="n">
-        <v>366.4133017357839</v>
+        <v>299.7944980689813</v>
       </c>
       <c r="D73" t="n">
-        <v>42.43088558018941</v>
+        <v>41.05974361845448</v>
       </c>
       <c r="E73" t="n">
-        <v>0.8002958468834436</v>
+        <v>1.063831320084121</v>
       </c>
       <c r="F73" t="n">
-        <v>9.672183962199092</v>
+        <v>7.890430962630369</v>
       </c>
       <c r="G73" t="n">
-        <v>0.7724461908803761</v>
+        <v>0.30265267877893</v>
       </c>
       <c r="H73" t="n">
-        <v>1.951027544541872e+21</v>
+        <v>4.039803016511461e+20</v>
       </c>
       <c r="I73" t="n">
-        <v>1.569154441398711e+21</v>
+        <v>4.300461545114571e+20</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1.06452258378385</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1.510545454545455</v>
+        <v>2.750545454545454</v>
       </c>
       <c r="B74" t="n">
-        <v>5398.152805714164</v>
+        <v>4235.258800262146</v>
       </c>
       <c r="C74" t="n">
-        <v>364.0341357929535</v>
+        <v>295.6281130507253</v>
       </c>
       <c r="D74" t="n">
-        <v>42.43187242755521</v>
+        <v>41.0343541398253</v>
       </c>
       <c r="E74" t="n">
-        <v>0.7995354506061134</v>
+        <v>1.054804046598906</v>
       </c>
       <c r="F74" t="n">
-        <v>9.640606411985397</v>
+        <v>7.878766726080734</v>
       </c>
       <c r="G74" t="n">
-        <v>0.7614318798003219</v>
+        <v>0.2957853314523046</v>
       </c>
       <c r="H74" t="n">
-        <v>1.946577897074915e+21</v>
+        <v>3.932703425446866e+20</v>
       </c>
       <c r="I74" t="n">
-        <v>1.563933370796664e+21</v>
+        <v>4.150858055687392e+20</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1.055471925197547</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1.531525252525253</v>
+        <v>2.788747474747475</v>
       </c>
       <c r="B75" t="n">
-        <v>5383.595074312664</v>
+        <v>4221.602069429974</v>
       </c>
       <c r="C75" t="n">
-        <v>362.7202600317686</v>
+        <v>287.8517181147896</v>
       </c>
       <c r="D75" t="n">
-        <v>42.43179725403376</v>
+        <v>41.01637400482785</v>
       </c>
       <c r="E75" t="n">
-        <v>0.8009640112022098</v>
+        <v>1.033713530326938</v>
       </c>
       <c r="F75" t="n">
-        <v>9.610272575806931</v>
+        <v>7.865174796151496</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7529173527181464</v>
+        <v>0.2849703493194008</v>
       </c>
       <c r="H75" t="n">
-        <v>1.940307191529739e+21</v>
+        <v>3.855961240465728e+20</v>
       </c>
       <c r="I75" t="n">
-        <v>1.561533015049635e+21</v>
+        <v>3.988406970298685e+20</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1.034348304242021</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1.552505050505051</v>
+        <v>2.826949494949495</v>
       </c>
       <c r="B76" t="n">
-        <v>5369.349551613992</v>
+        <v>4205.732045018564</v>
       </c>
       <c r="C76" t="n">
-        <v>362.3716105520215</v>
+        <v>282.9362450654185</v>
       </c>
       <c r="D76" t="n">
-        <v>42.43086873781054</v>
+        <v>41.00480814487272</v>
       </c>
       <c r="E76" t="n">
-        <v>0.8044457713411962</v>
+        <v>1.023743952897123</v>
       </c>
       <c r="F76" t="n">
-        <v>9.580812893640985</v>
+        <v>7.849560366635589</v>
       </c>
       <c r="G76" t="n">
-        <v>0.7465750099738369</v>
+        <v>0.2766577524047164</v>
       </c>
       <c r="H76" t="n">
-        <v>1.932564052267176e+21</v>
+        <v>3.804053581494618e+20</v>
       </c>
       <c r="I76" t="n">
-        <v>1.561919673681683e+21</v>
+        <v>3.896684084701947e+20</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1.024350472784596</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1.573484848484848</v>
+        <v>2.865151515151515</v>
       </c>
       <c r="B77" t="n">
-        <v>5355.210949468093</v>
+        <v>4183.977792745584</v>
       </c>
       <c r="C77" t="n">
-        <v>362.8704389055214</v>
+        <v>282.9943590818105</v>
       </c>
       <c r="D77" t="n">
-        <v>42.42936812297764</v>
+        <v>41.01036939018206</v>
       </c>
       <c r="E77" t="n">
-        <v>0.8098123337931799</v>
+        <v>1.034629840949584</v>
       </c>
       <c r="F77" t="n">
-        <v>9.551792337493032</v>
+        <v>7.828469341693242</v>
       </c>
       <c r="G77" t="n">
-        <v>0.7420370112107139</v>
+        <v>0.2720236992080401</v>
       </c>
       <c r="H77" t="n">
-        <v>1.923821178751342e+21</v>
+        <v>3.814989658565605e+20</v>
       </c>
       <c r="I77" t="n">
-        <v>1.565086258054092e+21</v>
+        <v>3.949327582844907e+20</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1.035213181765167</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1.594464646464647</v>
+        <v>2.903353535353535</v>
       </c>
       <c r="B78" t="n">
-        <v>5340.819466131005</v>
+        <v>4154.666494057599</v>
       </c>
       <c r="C78" t="n">
-        <v>364.0650531567343</v>
+        <v>285.5245534595679</v>
       </c>
       <c r="D78" t="n">
-        <v>42.4279429150512</v>
+        <v>41.03950601948101</v>
       </c>
       <c r="E78" t="n">
-        <v>0.8168628773722287</v>
+        <v>1.058661425135315</v>
       </c>
       <c r="F78" t="n">
-        <v>9.522475088238208</v>
+        <v>7.800619095920604</v>
       </c>
       <c r="G78" t="n">
-        <v>0.7388147617465255</v>
+        <v>0.2681424478811717</v>
       </c>
       <c r="H78" t="n">
-        <v>1.915184925156129e+21</v>
+        <v>3.913807481441651e+20</v>
       </c>
       <c r="I78" t="n">
-        <v>1.571484346515056e+21</v>
+        <v>4.145580595260124e+20</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1.059219344568553</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1.615444444444444</v>
+        <v>2.941555555555555</v>
       </c>
       <c r="B79" t="n">
-        <v>5325.866146087327</v>
+        <v>4116.867409943914</v>
       </c>
       <c r="C79" t="n">
-        <v>365.7815741762672</v>
+        <v>284.5632607730698</v>
       </c>
       <c r="D79" t="n">
-        <v>42.42710178493682</v>
+        <v>41.09568697935944</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8253293567743839</v>
+        <v>1.07456089406911</v>
       </c>
       <c r="F79" t="n">
-        <v>9.492250114222708</v>
+        <v>7.765654203247072</v>
       </c>
       <c r="G79" t="n">
-        <v>0.7364044895319836</v>
+        <v>0.2592331700821733</v>
       </c>
       <c r="H79" t="n">
-        <v>1.907500868479059e+21</v>
+        <v>4.121426090623953e+20</v>
       </c>
       <c r="I79" t="n">
-        <v>1.581256246474181e+21</v>
+        <v>4.43085982393281e+20</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1.075079287243026</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1.636424242424243</v>
+        <v>2.979757575757576</v>
       </c>
       <c r="B80" t="n">
-        <v>5310.476667226028</v>
+        <v>4074.067068995052</v>
       </c>
       <c r="C80" t="n">
-        <v>367.1273761911473</v>
+        <v>277.2580442054007</v>
       </c>
       <c r="D80" t="n">
-        <v>42.42665163282906</v>
+        <v>41.16806167232147</v>
       </c>
       <c r="E80" t="n">
-        <v>0.8331740277715979</v>
+        <v>1.069088775342287</v>
       </c>
       <c r="F80" t="n">
-        <v>9.461394750563564</v>
+        <v>7.727336380831679</v>
       </c>
       <c r="G80" t="n">
-        <v>0.7330480000218245</v>
+        <v>0.2438881417399273</v>
       </c>
       <c r="H80" t="n">
-        <v>1.900444693442791e+21</v>
+        <v>4.408909821109796e+20</v>
       </c>
       <c r="I80" t="n">
-        <v>1.590232535536663e+21</v>
+        <v>4.715569595245515e+20</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1.069554558060461</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1.65740404040404</v>
+        <v>3.017959595959596</v>
       </c>
       <c r="B81" t="n">
-        <v>5294.654835576003</v>
+        <v>4038.551427510219</v>
       </c>
       <c r="C81" t="n">
-        <v>367.3143474899389</v>
+        <v>275.1089493748913</v>
       </c>
       <c r="D81" t="n">
-        <v>42.42658743021821</v>
+        <v>41.22059643256117</v>
       </c>
       <c r="E81" t="n">
-        <v>0.8385878174739336</v>
+        <v>1.079541758004549</v>
       </c>
       <c r="F81" t="n">
-        <v>9.429937051222309</v>
+        <v>7.696550935813712</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7272049182851223</v>
+        <v>0.2349572236375904</v>
       </c>
       <c r="H81" t="n">
-        <v>1.894004399788176e+21</v>
+        <v>4.628210489126599e+20</v>
       </c>
       <c r="I81" t="n">
-        <v>1.594990688306808e+21</v>
+        <v>4.998343782650312e+20</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1.079973305966376</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1.678383838383839</v>
+        <v>3.056161616161616</v>
       </c>
       <c r="B82" t="n">
-        <v>5278.63007755208</v>
+        <v>4017.918794375752</v>
       </c>
       <c r="C82" t="n">
-        <v>366.698843314406</v>
+        <v>281.5392244051861</v>
       </c>
       <c r="D82" t="n">
-        <v>42.42654508762703</v>
+        <v>41.22708570634316</v>
       </c>
       <c r="E82" t="n">
-        <v>0.842273325446888</v>
+        <v>1.116149997806524</v>
       </c>
       <c r="F82" t="n">
-        <v>9.398348323821697</v>
+        <v>7.679081340446507</v>
       </c>
       <c r="G82" t="n">
-        <v>0.71972455111072</v>
+        <v>0.2363124608018407</v>
       </c>
       <c r="H82" t="n">
-        <v>1.887579872005836e+21</v>
+        <v>4.647768391147569e+20</v>
       </c>
       <c r="I82" t="n">
-        <v>1.596415959697456e+21</v>
+        <v>5.189578031315688e+20</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1.116574147971763</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1.699363636363636</v>
+        <v>3.094363636363636</v>
       </c>
       <c r="B83" t="n">
-        <v>5262.911185596288</v>
+        <v>4006.331833561534</v>
       </c>
       <c r="C83" t="n">
-        <v>366.1512833745776</v>
+        <v>281.6326403551118</v>
       </c>
       <c r="D83" t="n">
-        <v>42.42570452427341</v>
+        <v>41.19965837070957</v>
       </c>
       <c r="E83" t="n">
-        <v>0.8460469055813509</v>
+        <v>1.122987995996999</v>
       </c>
       <c r="F83" t="n">
-        <v>9.367627797495468</v>
+        <v>7.669403294598533</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7125402473334496</v>
+        <v>0.2340828016508398</v>
       </c>
       <c r="H83" t="n">
-        <v>1.879829130765909e+21</v>
+        <v>4.516325609748913e+20</v>
       </c>
       <c r="I83" t="n">
-        <v>1.596838351403557e+21</v>
+        <v>5.073652351055318e+20</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1.123402692689686</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1.720343434343434</v>
+        <v>3.132565656565657</v>
       </c>
       <c r="B84" t="n">
-        <v>5247.555699691404</v>
+        <v>3994.553153527967</v>
       </c>
       <c r="C84" t="n">
-        <v>365.6886421494929</v>
+        <v>280.0297164571928</v>
       </c>
       <c r="D84" t="n">
-        <v>42.42395168279472</v>
+        <v>41.16814577719362</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8499303168307386</v>
+        <v>1.123191154665704</v>
       </c>
       <c r="F84" t="n">
-        <v>9.337870452809792</v>
+        <v>7.659662153189491</v>
       </c>
       <c r="G84" t="n">
-        <v>0.7057015683586703</v>
+        <v>0.2304292607667419</v>
       </c>
       <c r="H84" t="n">
-        <v>1.870575939407352e+21</v>
+        <v>4.37066518577203e+20</v>
       </c>
       <c r="I84" t="n">
-        <v>1.596131873275596e+21</v>
+        <v>4.91085300096914e+20</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1.123593959325826</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1.741323232323232</v>
+        <v>3.170767676767677</v>
       </c>
       <c r="B85" t="n">
-        <v>5232.626679180274</v>
+        <v>3976.921008277265</v>
       </c>
       <c r="C85" t="n">
-        <v>365.3271883980977</v>
+        <v>277.6103991875441</v>
       </c>
       <c r="D85" t="n">
-        <v>42.42116077597082</v>
+        <v>41.15526856294923</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8539421588692874</v>
+        <v>1.123382783511661</v>
       </c>
       <c r="F85" t="n">
-        <v>9.309178086950107</v>
+        <v>7.645261894877662</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6992575931217224</v>
+        <v>0.22501544944009</v>
       </c>
       <c r="H85" t="n">
-        <v>1.859630936593832e+21</v>
+        <v>4.30663224953379e+20</v>
       </c>
       <c r="I85" t="n">
-        <v>1.594148977425232e+21</v>
+        <v>4.83965666690521e+20</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1.1237682686812</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1.76230303030303</v>
+        <v>3.208969696969697</v>
       </c>
       <c r="B86" t="n">
-        <v>5218.194678586206</v>
+        <v>3948.013867004844</v>
       </c>
       <c r="C86" t="n">
-        <v>365.0850197957042</v>
+        <v>274.8907811703513</v>
       </c>
       <c r="D86" t="n">
-        <v>42.41719087622305</v>
+        <v>41.18423375892745</v>
       </c>
       <c r="E86" t="n">
-        <v>0.8581030015604028</v>
+        <v>1.128726703009686</v>
       </c>
       <c r="F86" t="n">
-        <v>9.281663750827246</v>
+        <v>7.622121206956519</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6932625436768634</v>
+        <v>0.2173102431377816</v>
       </c>
       <c r="H86" t="n">
-        <v>1.846788448492751e+21</v>
+        <v>4.419780449536985e+20</v>
       </c>
       <c r="I86" t="n">
-        <v>1.590726703512989e+21</v>
+        <v>4.990315402266484e+20</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1.12908671804937</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1.783282828282828</v>
+        <v>3.247171717171717</v>
       </c>
       <c r="B87" t="n">
-        <v>5204.338501688366</v>
+        <v>3909.727538376881</v>
       </c>
       <c r="C87" t="n">
-        <v>364.98222660146</v>
+        <v>270.8859363277673</v>
       </c>
       <c r="D87" t="n">
-        <v>42.41188444596704</v>
+        <v>41.24564129676313</v>
       </c>
       <c r="E87" t="n">
-        <v>0.8624354638964282</v>
+        <v>1.134173340258385</v>
       </c>
       <c r="F87" t="n">
-        <v>9.25545267851186</v>
+        <v>7.592356010117607</v>
       </c>
       <c r="G87" t="n">
-        <v>0.6877766670586141</v>
+        <v>0.2070701712602213</v>
       </c>
       <c r="H87" t="n">
-        <v>1.831826888999259e+21</v>
+        <v>4.681341944337767e+20</v>
       </c>
       <c r="I87" t="n">
-        <v>1.585686079547123e+21</v>
+        <v>5.310988130026156e+20</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1.134501216355273</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1.804262626262626</v>
+        <v>3.285373737373738</v>
       </c>
       <c r="B88" t="n">
-        <v>5191.146002092391</v>
+        <v>3863.614576721336</v>
       </c>
       <c r="C88" t="n">
-        <v>365.0410595539349</v>
+        <v>264.4476128503683</v>
       </c>
       <c r="D88" t="n">
-        <v>42.40506581982487</v>
+        <v>41.33211400102169</v>
       </c>
       <c r="E88" t="n">
-        <v>0.8669642551362809</v>
+        <v>1.133804097417313</v>
       </c>
       <c r="F88" t="n">
-        <v>9.230683313564917</v>
+        <v>7.557820492733565</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6828662706339353</v>
+        <v>0.1939871746309514</v>
       </c>
       <c r="H88" t="n">
-        <v>1.814509827434369e+21</v>
+        <v>5.080950824930548e+20</v>
       </c>
       <c r="I88" t="n">
-        <v>1.578831834159935e+21</v>
+        <v>5.762278822875595e+20</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1.134094586116047</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1.825242424242424</v>
+        <v>3.323575757575758</v>
       </c>
       <c r="B89" t="n">
-        <v>5178.714924416114</v>
+        <v>3816.867369242344</v>
       </c>
       <c r="C89" t="n">
-        <v>365.2860989827072</v>
+        <v>262.4243285492816</v>
       </c>
       <c r="D89" t="n">
-        <v>42.39653966837782</v>
+        <v>41.42035743005088</v>
       </c>
       <c r="E89" t="n">
-        <v>0.8717161632017238</v>
+        <v>1.152858270301212</v>
       </c>
       <c r="F89" t="n">
-        <v>9.207509429396948</v>
+        <v>7.524247168427641</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6786052218863692</v>
+        <v>0.1844660963860503</v>
       </c>
       <c r="H89" t="n">
-        <v>1.79458810586124e+21</v>
+        <v>5.525035932044679e+20</v>
       </c>
       <c r="I89" t="n">
-        <v>1.56995276246526e+21</v>
+        <v>6.371023449591411e+20</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1.153118916863524</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1.846222222222222</v>
+        <v>3.361777777777778</v>
       </c>
       <c r="B90" t="n">
-        <v>5167.15916763973</v>
+        <v>3781.678035649063</v>
       </c>
       <c r="C90" t="n">
-        <v>365.7358411269458</v>
+        <v>266.8632092414396</v>
       </c>
       <c r="D90" t="n">
-        <v>42.3860805433244</v>
+        <v>41.47013174023036</v>
       </c>
       <c r="E90" t="n">
-        <v>0.8766975760515593</v>
+        <v>1.19427836562032</v>
       </c>
       <c r="F90" t="n">
-        <v>9.186111061767221</v>
+        <v>7.499910507560635</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6750614048207326</v>
+        <v>0.1815518204223927</v>
       </c>
       <c r="H90" t="n">
-        <v>1.77178884973709e+21</v>
+        <v>5.788217510811025e+20</v>
       </c>
       <c r="I90" t="n">
-        <v>1.558770455155281e+21</v>
+        <v>6.914162835510784e+20</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1.194523672028005</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1.86720202020202</v>
+        <v>3.399979797979798</v>
       </c>
       <c r="B91" t="n">
-        <v>5157.526075465998</v>
+        <v>3756.507535049215</v>
       </c>
       <c r="C91" t="n">
-        <v>364.9444444365689</v>
+        <v>271.5482917990912</v>
       </c>
       <c r="D91" t="n">
-        <v>42.37190535897146</v>
+        <v>41.48539922666382</v>
       </c>
       <c r="E91" t="n">
-        <v>0.8780714468282137</v>
+        <v>1.231585336538057</v>
       </c>
       <c r="F91" t="n">
-        <v>9.168378691818971</v>
+        <v>7.482987617568182</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6699676288136168</v>
+        <v>0.1804100992326057</v>
       </c>
       <c r="H91" t="n">
-        <v>1.7434785604722e+21</v>
+        <v>5.86400555752961e+20</v>
       </c>
       <c r="I91" t="n">
-        <v>1.536190857572743e+21</v>
+        <v>7.223406919682982e+20</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1.231821294986299</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1.888181818181818</v>
+        <v>3.438181818181818</v>
       </c>
       <c r="B92" t="n">
-        <v>5150.643852878232</v>
+        <v>3733.248657021044</v>
       </c>
       <c r="C92" t="n">
-        <v>361.836925248409</v>
+        <v>266.9389644448571</v>
       </c>
       <c r="D92" t="n">
-        <v>42.35257456627382</v>
+        <v>41.49143753810502</v>
       </c>
       <c r="E92" t="n">
-        <v>0.872922735510096</v>
+        <v>1.225812651092555</v>
       </c>
       <c r="F92" t="n">
-        <v>9.155768676906726</v>
+        <v>7.467704597349939</v>
       </c>
       <c r="G92" t="n">
-        <v>0.6616948000941381</v>
+        <v>0.1734614207333509</v>
       </c>
       <c r="H92" t="n">
-        <v>1.707747361660757e+21</v>
+        <v>5.887472371028663e+20</v>
       </c>
       <c r="I92" t="n">
-        <v>1.49583186439946e+21</v>
+        <v>7.218233704641195e+20</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1.226032709751812</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1.909161616161616</v>
+        <v>3.476383838383839</v>
       </c>
       <c r="B93" t="n">
-        <v>5146.609640231875</v>
+        <v>3704.279805686544</v>
       </c>
       <c r="C93" t="n">
-        <v>356.8831909871107</v>
+        <v>257.5248332058979</v>
       </c>
       <c r="D93" t="n">
-        <v>42.32819402060652</v>
+        <v>41.51356950443637</v>
       </c>
       <c r="E93" t="n">
-        <v>0.8623222617716311</v>
+        <v>1.201150729675406</v>
       </c>
       <c r="F93" t="n">
-        <v>9.148399658853563</v>
+        <v>7.449140057463985</v>
       </c>
       <c r="G93" t="n">
-        <v>0.6511531246623151</v>
+        <v>0.1627341039072343</v>
       </c>
       <c r="H93" t="n">
-        <v>1.665273626604646e+21</v>
+        <v>6.004262663740634e+20</v>
       </c>
       <c r="I93" t="n">
-        <v>1.440885941354629e+21</v>
+        <v>7.213217206963448e+20</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1.20134937642279</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1.930141414141414</v>
+        <v>3.514585858585859</v>
       </c>
       <c r="B94" t="n">
-        <v>5145.473801987433</v>
+        <v>3668.188666796928</v>
       </c>
       <c r="C94" t="n">
-        <v>350.8802797836808</v>
+        <v>246.0763192135351</v>
       </c>
       <c r="D94" t="n">
-        <v>42.29917223518919</v>
+        <v>41.55960829551957</v>
       </c>
       <c r="E94" t="n">
-        <v>0.8481920174288757</v>
+        <v>1.170448893731402</v>
       </c>
       <c r="F94" t="n">
-        <v>9.146327928703311</v>
+        <v>7.426730610498814</v>
       </c>
       <c r="G94" t="n">
-        <v>0.6397903800968792</v>
+        <v>0.1501004682879341</v>
       </c>
       <c r="H94" t="n">
-        <v>1.617272649785198e+21</v>
+        <v>6.268239860345269e+20</v>
       </c>
       <c r="I94" t="n">
-        <v>1.376414731547678e+21</v>
+        <v>7.337748113523544e+20</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1.170623377057457</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1.951121212121212</v>
+        <v>3.552787878787879</v>
       </c>
       <c r="B95" t="n">
-        <v>5147.352355617672</v>
+        <v>3622.371091695624</v>
       </c>
       <c r="C95" t="n">
-        <v>343.9364680572268</v>
+        <v>235.5027483753447</v>
       </c>
       <c r="D95" t="n">
-        <v>42.26528928864261</v>
+        <v>41.64390943769634</v>
       </c>
       <c r="E95" t="n">
-        <v>0.8307998191584939</v>
+        <v>1.148672077518263</v>
       </c>
       <c r="F95" t="n">
-        <v>9.149755062961749</v>
+        <v>7.399410372962917</v>
       </c>
       <c r="G95" t="n">
-        <v>0.6277940279274333</v>
+        <v>0.1372273072241414</v>
       </c>
       <c r="H95" t="n">
-        <v>1.563978452421858e+21</v>
+        <v>6.79448541443921e+20</v>
       </c>
       <c r="I95" t="n">
-        <v>1.303776669425569e+21</v>
+        <v>7.805652836186645e+20</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1.148821781204882</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1.97210101010101</v>
+        <v>3.590989898989899</v>
       </c>
       <c r="B96" t="n">
-        <v>5152.33769797557</v>
+        <v>3565.108443127413</v>
       </c>
       <c r="C96" t="n">
-        <v>336.1786518066829</v>
+        <v>229.0154607433029</v>
       </c>
       <c r="D96" t="n">
-        <v>42.22636884884817</v>
+        <v>41.77673895485542</v>
       </c>
       <c r="E96" t="n">
-        <v>0.8104896139032179</v>
+        <v>1.153201705176538</v>
       </c>
       <c r="F96" t="n">
-        <v>9.158867703681134</v>
+        <v>7.366998186958637</v>
       </c>
       <c r="G96" t="n">
-        <v>0.6153601181938069</v>
+        <v>0.1258488890069849</v>
       </c>
       <c r="H96" t="n">
-        <v>1.505775236768725e+21</v>
+        <v>7.725687655805931e+20</v>
       </c>
       <c r="I96" t="n">
-        <v>1.224601329071087e+21</v>
+        <v>8.910253630916991e+20</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1.153328224992483</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1.993080808080808</v>
+        <v>3.629191919191919</v>
       </c>
       <c r="B97" t="n">
-        <v>5160.496630482557</v>
+        <v>3491.230913397065</v>
       </c>
       <c r="C97" t="n">
-        <v>327.7614211654175</v>
+        <v>223.4645976775247</v>
       </c>
       <c r="D97" t="n">
-        <v>42.18229045088326</v>
+        <v>41.98263890380075</v>
       </c>
       <c r="E97" t="n">
-        <v>0.7876999163413686</v>
+        <v>1.173376926772991</v>
       </c>
       <c r="F97" t="n">
-        <v>9.173836613868502</v>
+        <v>7.327937121827272</v>
       </c>
       <c r="G97" t="n">
-        <v>0.6027121257868805</v>
+        <v>0.1135681813006192</v>
       </c>
       <c r="H97" t="n">
-        <v>1.443199470616108e+21</v>
+        <v>9.441685471227905e+20</v>
       </c>
       <c r="I97" t="n">
-        <v>1.140755401795755e+21</v>
+        <v>1.107962218388608e+21</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1.173479271010408</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2.014060606060606</v>
+        <v>3.667393939393939</v>
       </c>
       <c r="B98" t="n">
-        <v>5171.870793199566</v>
+        <v>3396.279201438882</v>
       </c>
       <c r="C98" t="n">
-        <v>318.8642161859688</v>
+        <v>208.3530690741235</v>
       </c>
       <c r="D98" t="n">
-        <v>42.13298893474061</v>
+        <v>42.28310907020592</v>
       </c>
       <c r="E98" t="n">
-        <v>0.7629505916259512</v>
+        <v>1.156056590611175</v>
       </c>
       <c r="F98" t="n">
-        <v>9.194819081342255</v>
+        <v>7.282105682595418</v>
       </c>
       <c r="G98" t="n">
-        <v>0.5901029388426847</v>
+        <v>0.09534536584815693</v>
       </c>
       <c r="H98" t="n">
-        <v>1.376915129017091e+21</v>
+        <v>1.267118720516875e+21</v>
       </c>
       <c r="I98" t="n">
-        <v>1.054228296144604e+21</v>
+        <v>1.464954894204709e+21</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1.156130732254618</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2.035040404040404</v>
+        <v>3.70559595959596</v>
       </c>
       <c r="B99" t="n">
-        <v>5186.478182651778</v>
+        <v>3281.221319680527</v>
       </c>
       <c r="C99" t="n">
-        <v>309.6874947408068</v>
+        <v>163.0739715039255</v>
       </c>
       <c r="D99" t="n">
-        <v>42.07845112273151</v>
+        <v>42.68414831348973</v>
       </c>
       <c r="E99" t="n">
-        <v>0.7368252854999224</v>
+        <v>0.9693922908757354</v>
       </c>
       <c r="F99" t="n">
-        <v>9.221962829711707</v>
+        <v>7.232804212586909</v>
       </c>
       <c r="G99" t="n">
-        <v>0.5778149496340537</v>
+        <v>0.06523909365276363</v>
       </c>
       <c r="H99" t="n">
-        <v>1.307681199691972e+21</v>
+        <v>1.879473338813483e+21</v>
       </c>
       <c r="I99" t="n">
-        <v>9.670099776708082e+20</v>
+        <v>1.822025833335087e+21</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.9694342535794294</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2.056020202020202</v>
+        <v>3.74379797979798</v>
       </c>
       <c r="B100" t="n">
-        <v>5204.31565364891</v>
+        <v>3140.977339828756</v>
       </c>
       <c r="C100" t="n">
-        <v>300.4482367496789</v>
+        <v>80.21286086654582</v>
       </c>
       <c r="D100" t="n">
-        <v>42.01870998425089</v>
+        <v>43.2271069491526</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7099509803913434</v>
+        <v>0.5203557555593876</v>
       </c>
       <c r="F100" t="n">
-        <v>9.255409619553664</v>
+        <v>7.181297967520445</v>
       </c>
       <c r="G100" t="n">
-        <v>0.5661609144699786</v>
+        <v>0.02691045736111582</v>
       </c>
       <c r="H100" t="n">
-        <v>1.23631434962583e+21</v>
+        <v>3.211710167075606e+21</v>
       </c>
       <c r="I100" t="n">
-        <v>8.809746197049935e+20</v>
+        <v>1.671275205408959e+21</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.5203692483032253</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2.077</v>
+        <v>3.782</v>
       </c>
       <c r="B101" t="n">
-        <v>5225.362259436593</v>
+        <v>2943.510822054942</v>
       </c>
       <c r="C101" t="n">
-        <v>291.3751740542384</v>
+        <v>70.02021292842474</v>
       </c>
       <c r="D101" t="n">
-        <v>41.95383668895239</v>
+        <v>44.10815237093693</v>
       </c>
       <c r="E101" t="n">
-        <v>0.6829764053424003</v>
+        <v>0.5172233422188319</v>
       </c>
       <c r="F101" t="n">
-        <v>9.295301295974026</v>
+        <v>7.123199226385925</v>
       </c>
       <c r="G101" t="n">
-        <v>0.5554849719302345</v>
+        <v>0.01785389952856597</v>
       </c>
       <c r="H101" t="n">
-        <v>1.163650667869686e+21</v>
+        <v>7.688500656023687e+21</v>
       </c>
       <c r="I101" t="n">
-        <v>7.977824673819062e+20</v>
+        <v>3.976718698444917e+21</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.5172294152474695</v>
       </c>
     </row>
   </sheetData>
